--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Página1 (1)" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>Hero</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Sojourn</t>
   </si>
   <si>
-    <t>Soldier 76</t>
+    <t>Soldier: 76</t>
   </si>
   <si>
     <t>Sombra</t>
@@ -153,12 +153,15 @@
   <si>
     <t>Zenyatta</t>
   </si>
+  <si>
+    <t>Soldier 76</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -181,8 +184,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,12 +200,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,12 +219,10 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -592,16 +591,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="C2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E2" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F2" s="3">
         <v>1.0</v>
@@ -610,10 +609,10 @@
         <v>1.0</v>
       </c>
       <c r="H2" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J2" s="3">
         <v>1.0</v>
@@ -622,10 +621,10 @@
         <v>1.0</v>
       </c>
       <c r="L2" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M2" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N2" s="3">
         <v>-1.0</v>
@@ -634,22 +633,22 @@
         <v>1.0</v>
       </c>
       <c r="P2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R2" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S2" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U2" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V2" s="3">
         <v>0.0</v>
@@ -658,16 +657,16 @@
         <v>1.0</v>
       </c>
       <c r="X2" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y2" s="3">
         <v>1.0</v>
       </c>
       <c r="Z2" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AB2" s="3">
         <v>1.0</v>
@@ -676,16 +675,16 @@
         <v>1.0</v>
       </c>
       <c r="AD2" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF2" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH2" s="3">
         <v>-1.0</v>
@@ -697,25 +696,25 @@
         <v>0.0</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL2" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM2" s="3">
         <v>0.0</v>
       </c>
       <c r="AN2" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO2" s="3">
         <v>-1.0</v>
       </c>
       <c r="AP2" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ2" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR2" s="3">
         <v>0.0</v>
@@ -738,7 +737,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="D3" s="3">
         <v>0.0</v>
@@ -878,58 +877,58 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C4" s="3">
         <v>0.0</v>
       </c>
       <c r="D4" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="E4" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F4" s="3">
         <v>0.0</v>
       </c>
       <c r="G4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I4" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J4" s="3">
         <v>-1.0</v>
       </c>
       <c r="K4" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="L4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M4" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O4" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q4" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="R4" s="3">
         <v>1.0</v>
       </c>
       <c r="S4" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T4" s="3">
         <v>-1.0</v>
@@ -938,7 +937,7 @@
         <v>0.0</v>
       </c>
       <c r="V4" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W4" s="3">
         <v>0.0</v>
@@ -947,16 +946,16 @@
         <v>0.0</v>
       </c>
       <c r="Y4" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Z4" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB4" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC4" s="3">
         <v>0.0</v>
@@ -971,25 +970,25 @@
         <v>0.0</v>
       </c>
       <c r="AG4" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH4" s="3">
         <v>0.0</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ4" s="3">
         <v>-1.0</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM4" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN4" s="3">
         <v>0.0</v>
@@ -998,7 +997,7 @@
         <v>-1.0</v>
       </c>
       <c r="AP4" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AQ4" s="3">
         <v>-1.0</v>
@@ -1007,13 +1006,13 @@
         <v>-1.0</v>
       </c>
       <c r="AS4" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT4" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1021,7 +1020,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C5" s="3">
         <v>0.0</v>
@@ -1030,7 +1029,7 @@
         <v>0.0</v>
       </c>
       <c r="E5" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="F5" s="3">
         <v>1.0</v>
@@ -1042,19 +1041,19 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J5" s="3">
         <v>-1.0</v>
       </c>
       <c r="K5" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="L5" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M5" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N5" s="3">
         <v>0.0</v>
@@ -1069,46 +1068,46 @@
         <v>0.0</v>
       </c>
       <c r="R5" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S5" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T5" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U5" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V5" s="3">
         <v>0.0</v>
       </c>
       <c r="W5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y5" s="3">
         <v>1.0</v>
       </c>
       <c r="Z5" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB5" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD5" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF5" s="3">
         <v>0.0</v>
@@ -1129,13 +1128,13 @@
         <v>1.0</v>
       </c>
       <c r="AL5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM5" s="3">
         <v>-1.0</v>
       </c>
       <c r="AN5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO5" s="3">
         <v>-1.0</v>
@@ -1144,19 +1143,19 @@
         <v>0.0</v>
       </c>
       <c r="AQ5" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR5" s="3">
         <v>-1.0</v>
       </c>
       <c r="AS5" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1164,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C6" s="3">
         <v>0.0</v>
@@ -1173,28 +1172,28 @@
         <v>0.0</v>
       </c>
       <c r="E6" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F6" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I6" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J6" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K6" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="M6" s="3">
         <v>-1.0</v>
@@ -1203,100 +1202,100 @@
         <v>-1.0</v>
       </c>
       <c r="O6" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R6" s="3">
         <v>0.0</v>
       </c>
       <c r="S6" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T6" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
       </c>
       <c r="V6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y6" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Z6" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA6" s="3">
         <v>0.0</v>
       </c>
       <c r="AB6" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC6" s="3">
         <v>1.0</v>
       </c>
       <c r="AD6" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE6" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF6" s="3">
         <v>0.0</v>
       </c>
       <c r="AG6" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH6" s="3">
         <v>-1.0</v>
       </c>
       <c r="AI6" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK6" s="3">
         <v>1.0</v>
       </c>
       <c r="AL6" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM6" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AN6" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AO6" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP6" s="3">
         <v>0.0</v>
       </c>
       <c r="AQ6" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AR6" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU6" s="3">
         <v>-1.0</v>
@@ -1307,43 +1306,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C7" s="3">
         <v>0.0</v>
       </c>
       <c r="D7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E7" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F7" s="3">
         <v>-1.0</v>
       </c>
       <c r="G7" s="3">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H7" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J7" s="3">
         <v>1.0</v>
       </c>
       <c r="K7" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="3">
         <v>1.0</v>
       </c>
       <c r="N7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O7" s="3">
         <v>0.0</v>
@@ -1352,46 +1351,46 @@
         <v>0.0</v>
       </c>
       <c r="Q7" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="R7" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S7" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T7" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U7" s="3">
         <v>-1.0</v>
       </c>
       <c r="V7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W7" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="X7" s="3">
         <v>0.0</v>
       </c>
       <c r="Y7" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z7" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA7" s="3">
         <v>-1.0</v>
       </c>
       <c r="AB7" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC7" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE7" s="3">
         <v>-1.0</v>
@@ -1403,19 +1402,19 @@
         <v>0.0</v>
       </c>
       <c r="AH7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AK7" s="3">
         <v>0.0</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM7" s="3">
         <v>0.0</v>
@@ -1427,7 +1426,7 @@
         <v>0.0</v>
       </c>
       <c r="AP7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ7" s="3">
         <v>1.0</v>
@@ -1436,13 +1435,13 @@
         <v>1.0</v>
       </c>
       <c r="AS7" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU7" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -1450,139 +1449,139 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C8" s="3">
         <v>0.0</v>
       </c>
       <c r="D8" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F8" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G8" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="I8" s="3">
         <v>-1.0</v>
       </c>
       <c r="J8" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K8" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="M8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P8" s="3">
         <v>1.0</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
       </c>
       <c r="S8" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T8" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U8" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W8" s="3">
         <v>0.0</v>
       </c>
       <c r="X8" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y8" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Z8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA8" s="3">
         <v>0.0</v>
       </c>
       <c r="AB8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC8" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF8" s="3">
         <v>0.0</v>
       </c>
       <c r="AG8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH8" s="3">
         <v>-1.0</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AK8" s="3">
         <v>1.0</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM8" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AQ8" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AR8" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS8" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT8" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU8" s="3">
         <v>0.0</v>
@@ -1599,7 +1598,7 @@
         <v>0.0</v>
       </c>
       <c r="D9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -1608,16 +1607,16 @@
         <v>1.0</v>
       </c>
       <c r="G9" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H9" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I9" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="J9" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K9" s="3">
         <v>1.0</v>
@@ -1626,7 +1625,7 @@
         <v>1.0</v>
       </c>
       <c r="M9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="3">
         <v>1.0</v>
@@ -1635,28 +1634,28 @@
         <v>1.0</v>
       </c>
       <c r="P9" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q9" s="3">
         <v>0.0</v>
       </c>
       <c r="R9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T9" s="3">
         <v>1.0</v>
       </c>
       <c r="U9" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X9" s="3">
         <v>0.0</v>
@@ -1668,7 +1667,7 @@
         <v>1.0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB9" s="3">
         <v>1.0</v>
@@ -1680,49 +1679,49 @@
         <v>1.0</v>
       </c>
       <c r="AE9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG9" s="3">
         <v>0.0</v>
       </c>
       <c r="AH9" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AI9" s="3">
         <v>1.0</v>
       </c>
       <c r="AJ9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AL9" s="3">
         <v>0.0</v>
       </c>
       <c r="AM9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO9" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP9" s="3">
         <v>1.0</v>
       </c>
       <c r="AQ9" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AR9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT9" s="3">
         <v>0.0</v>
@@ -1736,100 +1735,100 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C10" s="3">
         <v>0.0</v>
       </c>
       <c r="D10" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E10" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" s="3">
         <v>-1.0</v>
       </c>
       <c r="G10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I10" s="3">
         <v>1.0</v>
       </c>
       <c r="J10" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="K10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M10" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q10" s="3">
         <v>0.0</v>
       </c>
       <c r="R10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S10" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U10" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X10" s="3">
         <v>0.0</v>
       </c>
       <c r="Y10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA10" s="3">
         <v>-1.0</v>
       </c>
       <c r="AB10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF10" s="3">
         <v>-1.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH10" s="3">
         <v>1.0</v>
@@ -1838,37 +1837,37 @@
         <v>1.0</v>
       </c>
       <c r="AJ10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK10" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM10" s="3">
         <v>1.0</v>
       </c>
       <c r="AN10" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO10" s="3">
         <v>1.0</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR10" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS10" s="3">
         <v>2.0</v>
       </c>
       <c r="AT10" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU10" s="3">
         <v>1.0</v>
@@ -1891,31 +1890,31 @@
         <v>-1.0</v>
       </c>
       <c r="F11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H11" s="3">
         <v>-1.0</v>
       </c>
       <c r="I11" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J11" s="3">
         <v>1.0</v>
       </c>
       <c r="K11" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="L11" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M11" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O11" s="3">
         <v>1.0</v>
@@ -1924,34 +1923,34 @@
         <v>-1.0</v>
       </c>
       <c r="Q11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R11" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T11" s="3">
         <v>0.0</v>
       </c>
       <c r="U11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V11" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W11" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y11" s="3">
         <v>1.0</v>
       </c>
       <c r="Z11" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA11" s="3">
         <v>1.0</v>
@@ -1960,40 +1959,40 @@
         <v>1.0</v>
       </c>
       <c r="AC11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD11" s="3">
         <v>1.0</v>
       </c>
       <c r="AE11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH11" s="3">
         <v>1.0</v>
       </c>
       <c r="AI11" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ11" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK11" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AL11" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM11" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN11" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO11" s="3">
         <v>1.0</v>
@@ -2005,13 +2004,13 @@
         <v>1.0</v>
       </c>
       <c r="AR11" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS11" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT11" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU11" s="3">
         <v>1.0</v>
@@ -2022,7 +2021,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C12" s="3">
         <v>0.0</v>
@@ -2031,82 +2030,82 @@
         <v>0.0</v>
       </c>
       <c r="E12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J12" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="3">
         <v>-1.0</v>
       </c>
       <c r="L12" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="M12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N12" s="3">
         <v>1.0</v>
       </c>
       <c r="O12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P12" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R12" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S12" s="3">
         <v>0.0</v>
       </c>
       <c r="T12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y12" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA12" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC12" s="3">
         <v>-1.0</v>
       </c>
       <c r="AD12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE12" s="3">
         <v>-1.0</v>
@@ -2115,22 +2114,22 @@
         <v>-1.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AI12" s="3">
         <v>0.0</v>
       </c>
       <c r="AJ12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK12" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL12" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM12" s="3">
         <v>0.0</v>
@@ -2139,25 +2138,25 @@
         <v>-1.0</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP12" s="3">
         <v>0.0</v>
       </c>
       <c r="AQ12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS12" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU12" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -2171,91 +2170,91 @@
         <v>0.0</v>
       </c>
       <c r="D13" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F13" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J13" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K13" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
       </c>
       <c r="M13" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O13" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P13" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q13" s="3">
         <v>0.0</v>
       </c>
       <c r="R13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S13" s="3">
         <v>0.0</v>
       </c>
       <c r="T13" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U13" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V13" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W13" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X13" s="3">
         <v>-1.0</v>
       </c>
       <c r="Y13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z13" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB13" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD13" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE13" s="3">
         <v>-1.0</v>
       </c>
       <c r="AF13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG13" s="3">
         <v>-1.0</v>
@@ -2264,16 +2263,16 @@
         <v>1.0</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ13" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK13" s="3">
         <v>-1.0</v>
       </c>
       <c r="AL13" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM13" s="3">
         <v>1.0</v>
@@ -2282,22 +2281,22 @@
         <v>-1.0</v>
       </c>
       <c r="AO13" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ13" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR13" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS13" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU13" s="3">
         <v>1.0</v>
@@ -2308,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="C14" s="3">
         <v>0.0</v>
@@ -2320,79 +2319,79 @@
         <v>0.0</v>
       </c>
       <c r="F14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K14" s="3">
         <v>0.0</v>
       </c>
       <c r="L14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M14" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N14" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="O14" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R14" s="3">
         <v>0.0</v>
       </c>
       <c r="S14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T14" s="3">
         <v>0.0</v>
       </c>
       <c r="U14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V14" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="W14" s="3">
         <v>1.0</v>
       </c>
       <c r="X14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA14" s="3">
         <v>1.0</v>
       </c>
       <c r="AB14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC14" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AD14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE14" s="3">
         <v>0.0</v>
@@ -2401,25 +2400,25 @@
         <v>0.0</v>
       </c>
       <c r="AG14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AM14" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN14" s="3">
         <v>0.0</v>
@@ -2428,19 +2427,19 @@
         <v>0.0</v>
       </c>
       <c r="AP14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ14" s="3">
         <v>0.0</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS14" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT14" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU14" s="3">
         <v>0.0</v>
@@ -2451,19 +2450,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C15" s="3">
         <v>0.0</v>
       </c>
       <c r="D15" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E15" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G15" s="3">
         <v>0.0</v>
@@ -2472,46 +2471,46 @@
         <v>0.0</v>
       </c>
       <c r="I15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O15" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R15" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U15" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W15" s="3">
         <v>0.0</v>
@@ -2520,22 +2519,22 @@
         <v>-1.0</v>
       </c>
       <c r="Y15" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z15" s="3">
         <v>0.0</v>
       </c>
       <c r="AA15" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC15" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE15" s="3">
         <v>0.0</v>
@@ -2544,7 +2543,7 @@
         <v>-1.0</v>
       </c>
       <c r="AG15" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH15" s="3">
         <v>1.0</v>
@@ -2553,37 +2552,37 @@
         <v>0.0</v>
       </c>
       <c r="AJ15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK15" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL15" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN15" s="3">
         <v>0.0</v>
       </c>
       <c r="AO15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP15" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR15" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS15" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU15" s="3">
         <v>0.0</v>
@@ -2600,13 +2599,13 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="3">
         <v>0.0</v>
@@ -2615,13 +2614,13 @@
         <v>-1.0</v>
       </c>
       <c r="I16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K16" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="3">
         <v>-1.0</v>
@@ -2630,25 +2629,25 @@
         <v>-1.0</v>
       </c>
       <c r="N16" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O16" s="3">
         <v>-1.0</v>
       </c>
       <c r="P16" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q16" s="3">
         <v>0.0</v>
       </c>
       <c r="R16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S16" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U16" s="3">
         <v>1.0</v>
@@ -2660,7 +2659,7 @@
         <v>0.0</v>
       </c>
       <c r="X16" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y16" s="3">
         <v>1.0</v>
@@ -2669,10 +2668,10 @@
         <v>0.0</v>
       </c>
       <c r="AA16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB16" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC16" s="3">
         <v>0.0</v>
@@ -2684,25 +2683,25 @@
         <v>0.0</v>
       </c>
       <c r="AF16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH16" s="3">
         <v>-1.0</v>
       </c>
       <c r="AI16" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK16" s="3">
         <v>1.0</v>
       </c>
       <c r="AL16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM16" s="3">
         <v>-1.0</v>
@@ -2711,25 +2710,25 @@
         <v>0.0</v>
       </c>
       <c r="AO16" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT16" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU16" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -2752,97 +2751,97 @@
         <v>0.0</v>
       </c>
       <c r="G17" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" s="3">
         <v>-1.0</v>
       </c>
       <c r="I17" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="3">
         <v>0.0</v>
       </c>
       <c r="K17" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L17" s="3">
         <v>0.0</v>
       </c>
       <c r="M17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P17" s="3">
         <v>0.0</v>
       </c>
       <c r="Q17" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="R17" s="3">
         <v>-1.0</v>
       </c>
       <c r="S17" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U17" s="3">
         <v>0.0</v>
       </c>
       <c r="V17" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W17" s="3">
         <v>0.0</v>
       </c>
       <c r="X17" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y17" s="3">
         <v>0.0</v>
       </c>
       <c r="Z17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA17" s="3">
         <v>0.0</v>
       </c>
       <c r="AB17" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC17" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD17" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE17" s="3">
         <v>0.0</v>
       </c>
       <c r="AF17" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG17" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AI17" s="3">
         <v>-1.0</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK17" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL17" s="3">
         <v>0.0</v>
@@ -2866,10 +2865,10 @@
         <v>0.0</v>
       </c>
       <c r="AS17" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT17" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU17" s="3">
         <v>-1.0</v>
@@ -2886,25 +2885,25 @@
         <v>0.0</v>
       </c>
       <c r="D18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E18" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I18" s="3">
         <v>0.0</v>
       </c>
       <c r="J18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="K18" s="3">
         <v>-1.0</v>
@@ -2913,22 +2912,22 @@
         <v>-1.0</v>
       </c>
       <c r="M18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N18" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O18" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P18" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q18" s="3">
         <v>0.0</v>
       </c>
       <c r="R18" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="S18" s="3">
         <v>-1.0</v>
@@ -2937,43 +2936,43 @@
         <v>0.0</v>
       </c>
       <c r="U18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="W18" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X18" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Y18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB18" s="3">
         <v>-1.0</v>
       </c>
       <c r="AC18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE18" s="3">
         <v>0.0</v>
       </c>
       <c r="AF18" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG18" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH18" s="3">
         <v>-1.0</v>
@@ -2985,37 +2984,37 @@
         <v>0.0</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AL18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
       </c>
       <c r="AO18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP18" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AQ18" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AR18" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT18" s="3">
         <v>0.0</v>
       </c>
       <c r="AU18" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -3023,7 +3022,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C19" s="3">
         <v>0.0</v>
@@ -3032,22 +3031,22 @@
         <v>-1.0</v>
       </c>
       <c r="E19" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F19" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G19" s="3">
         <v>1.0</v>
       </c>
       <c r="H19" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I19" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K19" s="3">
         <v>0.0</v>
@@ -3059,22 +3058,22 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O19" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P19" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q19" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R19" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S19" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="T19" s="3">
         <v>0.0</v>
@@ -3086,16 +3085,16 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X19" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y19" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Z19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA19" s="3">
         <v>1.0</v>
@@ -3107,55 +3106,55 @@
         <v>1.0</v>
       </c>
       <c r="AD19" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE19" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF19" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG19" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH19" s="3">
         <v>0.0</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK19" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL19" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM19" s="3">
         <v>0.0</v>
       </c>
       <c r="AN19" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP19" s="3">
         <v>-1.0</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AT19" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU19" s="3">
         <v>1.0</v>
@@ -3166,28 +3165,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C20" s="3">
         <v>0.0</v>
       </c>
       <c r="D20" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E20" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" s="3">
         <v>-1.0</v>
       </c>
       <c r="H20" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J20" s="3">
         <v>1.0</v>
@@ -3208,85 +3207,85 @@
         <v>2.0</v>
       </c>
       <c r="P20" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R20" s="3">
         <v>0.0</v>
       </c>
       <c r="S20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T20" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="U20" s="3">
         <v>-1.0</v>
       </c>
       <c r="V20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X20" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Y20" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z20" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA20" s="3">
         <v>0.0</v>
       </c>
       <c r="AB20" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE20" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF20" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG20" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH20" s="3">
         <v>0.0</v>
       </c>
       <c r="AI20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ20" s="3">
         <v>1.0</v>
       </c>
       <c r="AK20" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AL20" s="3">
         <v>-1.0</v>
       </c>
       <c r="AM20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO20" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP20" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ20" s="3">
         <v>1.0</v>
@@ -3295,7 +3294,7 @@
         <v>1.0</v>
       </c>
       <c r="AS20" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT20" s="3">
         <v>-1.0</v>
@@ -3309,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C21" s="3">
         <v>0.0</v>
@@ -3321,19 +3320,19 @@
         <v>0.0</v>
       </c>
       <c r="F21" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="3">
         <v>-1.0</v>
@@ -3345,13 +3344,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O21" s="3">
         <v>1.0</v>
       </c>
       <c r="P21" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q21" s="3">
         <v>0.0</v>
@@ -3360,34 +3359,34 @@
         <v>1.0</v>
       </c>
       <c r="S21" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T21" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U21" s="3">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V21" s="3">
         <v>-1.0</v>
       </c>
       <c r="W21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X21" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Y21" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z21" s="3">
         <v>-1.0</v>
       </c>
       <c r="AA21" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AB21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC21" s="3">
         <v>1.0</v>
@@ -3411,16 +3410,16 @@
         <v>0.0</v>
       </c>
       <c r="AJ21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL21" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM21" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -3429,22 +3428,22 @@
         <v>0.0</v>
       </c>
       <c r="AP21" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AQ21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR21" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS21" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AU21" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -3452,79 +3451,77 @@
         <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C22" s="3">
         <v>0.0</v>
       </c>
       <c r="D22" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E22" s="3">
         <v>1.0</v>
       </c>
       <c r="F22" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H22" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K22" s="3">
         <v>0.0</v>
       </c>
       <c r="L22" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="4"/>
       <c r="P22" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R22" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S22" s="3">
         <v>0.0</v>
       </c>
       <c r="T22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U22" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V22" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="W22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X22" s="3">
         <v>1.0</v>
       </c>
       <c r="Y22" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z22" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA22" s="3">
         <v>1.0</v>
@@ -3533,22 +3530,22 @@
         <v>0.0</v>
       </c>
       <c r="AC22" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD22" s="3">
         <v>1.0</v>
       </c>
       <c r="AE22" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AI22" s="3">
         <v>1.0</v>
@@ -3566,28 +3563,28 @@
         <v>1.0</v>
       </c>
       <c r="AN22" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO22" s="3">
         <v>1.0</v>
       </c>
       <c r="AP22" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT22" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU22" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -3595,7 +3592,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C23" s="3">
         <v>0.0</v>
@@ -3613,7 +3610,7 @@
         <v>-1.0</v>
       </c>
       <c r="H23" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23" s="3">
         <v>0.0</v>
@@ -3625,13 +3622,13 @@
         <v>1.0</v>
       </c>
       <c r="L23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N23" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O23" s="3">
         <v>0.0</v>
@@ -3640,73 +3637,73 @@
         <v>0.0</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="3">
         <v>0.0</v>
       </c>
       <c r="U23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W23" s="3">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Z23" s="3">
         <v>0.0</v>
       </c>
       <c r="AA23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB23" s="3">
         <v>1.0</v>
       </c>
       <c r="AC23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE23" s="3">
         <v>0.0</v>
       </c>
       <c r="AF23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AI23" s="3">
         <v>0.0</v>
       </c>
       <c r="AJ23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN23" s="3">
         <v>0.0</v>
@@ -3721,16 +3718,16 @@
         <v>1.0</v>
       </c>
       <c r="AR23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS23" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT23" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU23" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -3738,7 +3735,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="3">
         <v>0.0</v>
@@ -3750,34 +3747,34 @@
         <v>1.0</v>
       </c>
       <c r="F24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" s="3">
         <v>1.0</v>
       </c>
       <c r="I24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J24" s="3">
         <v>0.0</v>
       </c>
       <c r="K24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N24" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P24" s="3">
         <v>1.0</v>
@@ -3786,25 +3783,25 @@
         <v>1.0</v>
       </c>
       <c r="R24" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T24" s="3">
         <v>-1.0</v>
       </c>
       <c r="U24" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="V24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X24" s="3">
-        <v>-10.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y24" s="3">
         <v>0.0</v>
@@ -3813,7 +3810,7 @@
         <v>1.0</v>
       </c>
       <c r="AA24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB24" s="3">
         <v>-1.0</v>
@@ -3825,52 +3822,52 @@
         <v>1.0</v>
       </c>
       <c r="AE24" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG24" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AH24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AK24" s="3">
         <v>1.0</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AM24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN24" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP24" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ24" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR24" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS24" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT24" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU24" s="3">
         <v>0.0</v>
@@ -3881,49 +3878,49 @@
         <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C25" s="3">
         <v>0.0</v>
       </c>
       <c r="D25" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E25" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G25" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I25" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J25" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K25" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L25" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M25" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N25" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q25" s="3">
         <v>0.0</v>
@@ -3932,85 +3929,85 @@
         <v>1.0</v>
       </c>
       <c r="S25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T25" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U25" s="3">
         <v>0.0</v>
       </c>
       <c r="V25" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="W25" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X25" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y25" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z25" s="3">
         <v>-1.0</v>
       </c>
       <c r="AA25" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB25" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC25" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD25" s="3">
         <v>0.0</v>
       </c>
       <c r="AE25" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF25" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG25" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH25" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI25" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ25" s="3">
         <v>-1.0</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM25" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AN25" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO25" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP25" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ25" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR25" s="3">
         <v>0.0</v>
       </c>
       <c r="AS25" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT25" s="3">
         <v>1.0</v>
@@ -4024,7 +4021,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C26" s="3">
         <v>0.0</v>
@@ -4036,37 +4033,37 @@
         <v>-1.0</v>
       </c>
       <c r="F26" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G26" s="3">
         <v>-1.0</v>
       </c>
       <c r="H26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I26" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L26" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M26" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="3">
         <v>0.0</v>
       </c>
       <c r="P26" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="3">
         <v>0.0</v>
@@ -4075,28 +4072,28 @@
         <v>0.0</v>
       </c>
       <c r="S26" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T26" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U26" s="3">
         <v>-1.0</v>
       </c>
       <c r="V26" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z26" s="3">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA26" s="3">
         <v>0.0</v>
@@ -4105,22 +4102,22 @@
         <v>-1.0</v>
       </c>
       <c r="AC26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AD26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF26" s="3">
         <v>-1.0</v>
       </c>
       <c r="AG26" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH26" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AI26" s="3">
         <v>0.0</v>
@@ -4132,19 +4129,19 @@
         <v>1.0</v>
       </c>
       <c r="AL26" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM26" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN26" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO26" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ26" s="3">
         <v>1.0</v>
@@ -4153,10 +4150,10 @@
         <v>1.0</v>
       </c>
       <c r="AS26" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT26" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU26" s="3">
         <v>0.0</v>
@@ -4167,85 +4164,85 @@
         <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C27" s="3">
         <v>0.0</v>
       </c>
       <c r="D27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="K27" s="3">
         <v>0.0</v>
       </c>
       <c r="L27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="3">
         <v>0.0</v>
       </c>
       <c r="O27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P27" s="3">
         <v>1.0</v>
       </c>
       <c r="Q27" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="R27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U27" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y27" s="3">
         <v>0.0</v>
       </c>
       <c r="Z27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA27" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB27" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC27" s="3">
         <v>1.0</v>
@@ -4254,52 +4251,52 @@
         <v>1.0</v>
       </c>
       <c r="AE27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF27" s="3">
         <v>1.0</v>
       </c>
       <c r="AG27" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH27" s="3">
         <v>-1.0</v>
       </c>
       <c r="AI27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ27" s="3">
         <v>0.0</v>
       </c>
       <c r="AK27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL27" s="3">
         <v>1.0</v>
       </c>
       <c r="AM27" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AN27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO27" s="3">
         <v>0.0</v>
       </c>
       <c r="AP27" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ27" s="3">
         <v>0.0</v>
       </c>
       <c r="AR27" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS27" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT27" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU27" s="3">
         <v>0.0</v>
@@ -4322,31 +4319,31 @@
         <v>-1.0</v>
       </c>
       <c r="F28" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H28" s="3">
         <v>-1.0</v>
       </c>
       <c r="I28" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J28" s="3">
         <v>1.0</v>
       </c>
       <c r="K28" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L28" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M28" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="O28" s="3">
         <v>1.0</v>
@@ -4355,52 +4352,52 @@
         <v>-1.0</v>
       </c>
       <c r="Q28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="R28" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S28" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T28" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V28" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W28" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y28" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA28" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AB28" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC28" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AD28" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AE28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG28" s="3">
         <v>1.0</v>
@@ -4409,22 +4406,22 @@
         <v>1.0</v>
       </c>
       <c r="AI28" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ28" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK28" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AL28" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM28" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN28" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO28" s="3">
         <v>1.0</v>
@@ -4436,13 +4433,13 @@
         <v>0.0</v>
       </c>
       <c r="AR28" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS28" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT28" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU28" s="3">
         <v>0.0</v>
@@ -4453,7 +4450,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C29" s="3">
         <v>0.0</v>
@@ -4462,85 +4459,85 @@
         <v>0.0</v>
       </c>
       <c r="E29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G29" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" s="3">
         <v>0.0</v>
       </c>
       <c r="J29" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L29" s="3">
         <v>-1.0</v>
       </c>
       <c r="M29" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P29" s="3">
         <v>0.0</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="R29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S29" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W29" s="3">
         <v>1.0</v>
       </c>
       <c r="X29" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA29" s="3">
         <v>0.0</v>
       </c>
       <c r="AB29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC29" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD29" s="3">
         <v>1.0</v>
       </c>
       <c r="AE29" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF29" s="3">
         <v>0.0</v>
@@ -4555,7 +4552,7 @@
         <v>0.0</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK29" s="3">
         <v>1.0</v>
@@ -4567,7 +4564,7 @@
         <v>0.0</v>
       </c>
       <c r="AN29" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO29" s="3">
         <v>0.0</v>
@@ -4579,13 +4576,13 @@
         <v>0.0</v>
       </c>
       <c r="AR29" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS29" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT29" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU29" s="3">
         <v>0.0</v>
@@ -4596,46 +4593,46 @@
         <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C30" s="3">
         <v>0.0</v>
       </c>
       <c r="D30" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E30" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="3">
         <v>0.0</v>
       </c>
       <c r="H30" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K30" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="L30" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="M30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="3">
         <v>-1.0</v>
       </c>
       <c r="O30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P30" s="3">
         <v>0.0</v>
@@ -4644,91 +4641,91 @@
         <v>1.0</v>
       </c>
       <c r="R30" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U30" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W30" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="X30" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y30" s="3">
         <v>0.0</v>
       </c>
       <c r="Z30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB30" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AC30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD30" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE30" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF30" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH30" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AI30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK30" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL30" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM30" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AN30" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP30" s="3">
         <v>0.0</v>
       </c>
       <c r="AQ30" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AR30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS30" s="3">
-        <v>2.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT30" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU30" s="3">
         <v>1.0</v>
@@ -4745,25 +4742,25 @@
         <v>0.0</v>
       </c>
       <c r="D31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E31" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G31" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H31" s="3">
         <v>1.0</v>
       </c>
       <c r="I31" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K31" s="3">
         <v>-1.0</v>
@@ -4772,40 +4769,40 @@
         <v>-1.0</v>
       </c>
       <c r="M31" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q31" s="3">
         <v>0.0</v>
       </c>
       <c r="R31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S31" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U31" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V31" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W31" s="3">
         <v>0.0</v>
       </c>
       <c r="X31" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y31" s="3">
         <v>-1.0</v>
@@ -4814,7 +4811,7 @@
         <v>0.0</v>
       </c>
       <c r="AA31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AB31" s="3">
         <v>-1.0</v>
@@ -4826,10 +4823,10 @@
         <v>1.0</v>
       </c>
       <c r="AE31" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF31" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG31" s="3">
         <v>1.0</v>
@@ -4838,43 +4835,43 @@
         <v>0.0</v>
       </c>
       <c r="AI31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK31" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL31" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM31" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AN31" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO31" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP31" s="3">
         <v>-1.0</v>
       </c>
       <c r="AQ31" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR31" s="3">
         <v>-1.0</v>
       </c>
       <c r="AS31" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT31" s="3">
         <v>2.0</v>
       </c>
       <c r="AU31" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -4882,7 +4879,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C32" s="3">
         <v>0.0</v>
@@ -4894,46 +4891,46 @@
         <v>0.0</v>
       </c>
       <c r="F32" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G32" s="3">
         <v>0.0</v>
       </c>
       <c r="H32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I32" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="K32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="M32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="3">
         <v>0.0</v>
       </c>
       <c r="O32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="P32" s="3">
         <v>1.0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="R32" s="3">
         <v>1.0</v>
       </c>
       <c r="S32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="3">
         <v>0.0</v>
@@ -4948,73 +4945,73 @@
         <v>0.0</v>
       </c>
       <c r="X32" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y32" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA32" s="3">
         <v>0.0</v>
       </c>
       <c r="AB32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC32" s="3">
         <v>1.0</v>
       </c>
       <c r="AD32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE32" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF32" s="3">
-        <v>-10.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG32" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AH32" s="3">
         <v>-1.0</v>
       </c>
       <c r="AI32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AK32" s="3">
         <v>1.0</v>
       </c>
       <c r="AL32" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AM32" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN32" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO32" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP32" s="3">
         <v>-1.0</v>
       </c>
       <c r="AQ32" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AR32" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS32" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT32" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU32" s="3">
         <v>-1.0</v>
@@ -5025,7 +5022,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C33" s="3">
         <v>0.0</v>
@@ -5034,10 +5031,10 @@
         <v>1.0</v>
       </c>
       <c r="E33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F33" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G33" s="3">
         <v>0.0</v>
@@ -5049,22 +5046,22 @@
         <v>0.0</v>
       </c>
       <c r="J33" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L33" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M33" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N33" s="3">
         <v>1.0</v>
       </c>
       <c r="O33" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P33" s="3">
         <v>1.0</v>
@@ -5076,91 +5073,91 @@
         <v>1.0</v>
       </c>
       <c r="S33" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T33" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U33" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W33" s="3">
         <v>1.0</v>
       </c>
       <c r="X33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z33" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA33" s="3">
         <v>1.0</v>
       </c>
       <c r="AB33" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD33" s="3">
         <v>1.0</v>
       </c>
       <c r="AE33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG33" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH33" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AI33" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AL33" s="3">
         <v>1.0</v>
       </c>
       <c r="AM33" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO33" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP33" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ33" s="3">
         <v>0.0</v>
       </c>
       <c r="AR33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS33" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU33" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -5168,7 +5165,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C34" s="3">
         <v>0.0</v>
@@ -5180,28 +5177,28 @@
         <v>0.0</v>
       </c>
       <c r="F34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K34" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L34" s="3">
         <v>0.0</v>
       </c>
       <c r="M34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N34" s="3">
         <v>0.0</v>
@@ -5210,168 +5207,168 @@
         <v>1.0</v>
       </c>
       <c r="P34" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q34" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S34" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T34" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U34" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V34" s="3">
         <v>0.0</v>
       </c>
       <c r="W34" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y34" s="3">
         <v>1.0</v>
       </c>
       <c r="Z34" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB34" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC34" s="3">
         <v>0.0</v>
       </c>
       <c r="AD34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE34" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG34" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH34" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI34" s="3">
         <v>0.0</v>
       </c>
       <c r="AJ34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK34" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AL34" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AM34" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN34" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP34" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR34" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS34" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT34" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU34" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C35" s="3">
         <v>0.0</v>
       </c>
       <c r="D35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E35" s="3">
         <v>0.0</v>
       </c>
       <c r="F35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J35" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K35" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L35" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" s="3">
         <v>0.0</v>
       </c>
       <c r="N35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q35" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="R35" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S35" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W35" s="3">
         <v>0.0</v>
@@ -5386,7 +5383,7 @@
         <v>0.0</v>
       </c>
       <c r="AA35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB35" s="3">
         <v>1.0</v>
@@ -5395,58 +5392,58 @@
         <v>0.0</v>
       </c>
       <c r="AD35" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE35" s="3">
         <v>0.0</v>
       </c>
       <c r="AF35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH35" s="3">
         <v>0.0</v>
       </c>
       <c r="AI35" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK35" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL35" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM35" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN35" s="3">
         <v>0.0</v>
       </c>
       <c r="AO35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP35" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AQ35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS35" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT35" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU35" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -5454,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C36" s="3">
         <v>0.0</v>
@@ -5463,25 +5460,25 @@
         <v>-1.0</v>
       </c>
       <c r="E36" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F36" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="H36" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I36" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="J36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L36" s="3">
         <v>1.0</v>
@@ -5496,100 +5493,100 @@
         <v>1.0</v>
       </c>
       <c r="P36" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q36" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="R36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="S36" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T36" s="3">
         <v>1.0</v>
       </c>
       <c r="U36" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V36" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="W36" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="Y36" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Z36" s="3">
         <v>1.0</v>
       </c>
       <c r="AA36" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB36" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC36" s="3">
         <v>0.0</v>
       </c>
       <c r="AD36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AE36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AF36" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AG36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AH36" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AI36" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ36" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK36" s="3">
         <v>-1.0</v>
       </c>
       <c r="AL36" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AM36" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN36" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AO36" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AP36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AR36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AS36" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT36" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU36" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -5597,79 +5594,79 @@
         <v>36</v>
       </c>
       <c r="B37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C37" s="3">
         <v>0.0</v>
       </c>
       <c r="D37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E37" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G37" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I37" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J37" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="K37" s="3">
         <v>-1.0</v>
       </c>
       <c r="L37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M37" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P37" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q37" s="3">
         <v>1.0</v>
       </c>
       <c r="R37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S37" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T37" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U37" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="X37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA37" s="3">
         <v>1.0</v>
@@ -5678,16 +5675,16 @@
         <v>-1.0</v>
       </c>
       <c r="AC37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE37" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG37" s="3">
         <v>1.0</v>
@@ -5696,31 +5693,31 @@
         <v>-1.0</v>
       </c>
       <c r="AI37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK37" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL37" s="3">
         <v>1.0</v>
       </c>
       <c r="AM37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN37" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ37" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR37" s="3">
         <v>-1.0</v>
@@ -5729,10 +5726,10 @@
         <v>0.0</v>
       </c>
       <c r="AT37" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU37" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -5740,142 +5737,142 @@
         <v>37</v>
       </c>
       <c r="B38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C38" s="3">
         <v>0.0</v>
       </c>
       <c r="D38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F38" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G38" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H38" s="3">
         <v>1.0</v>
       </c>
       <c r="I38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="J38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="K38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="L38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N38" s="3">
         <v>-1.0</v>
       </c>
       <c r="O38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="P38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q38" s="3">
         <v>0.0</v>
       </c>
       <c r="R38" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U38" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V38" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="W38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X38" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y38" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Z38" s="3">
         <v>0.0</v>
       </c>
       <c r="AA38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC38" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE38" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF38" s="3">
         <v>1.0</v>
       </c>
       <c r="AG38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AK38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL38" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN38" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO38" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP38" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AR38" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS38" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT38" s="3">
         <v>0.0</v>
       </c>
       <c r="AU38" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -5889,40 +5886,40 @@
         <v>0.0</v>
       </c>
       <c r="D39" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E39" s="3">
         <v>-1.0</v>
       </c>
       <c r="F39" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="G39" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="H39" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="I39" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="J39" s="3">
         <v>1.0</v>
       </c>
       <c r="K39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L39" s="3">
         <v>0.0</v>
       </c>
       <c r="M39" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N39" s="3">
         <v>0.0</v>
       </c>
       <c r="O39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P39" s="3">
         <v>-1.0</v>
@@ -5931,91 +5928,91 @@
         <v>0.0</v>
       </c>
       <c r="R39" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S39" s="3">
         <v>0.0</v>
       </c>
       <c r="T39" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="U39" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V39" s="3">
         <v>1.0</v>
       </c>
       <c r="W39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X39" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="Y39" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Z39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA39" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AB39" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AC39" s="3">
         <v>0.0</v>
       </c>
       <c r="AD39" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AE39" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF39" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG39" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK39" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL39" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AM39" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN39" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AO39" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP39" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ39" s="3">
         <v>1.0</v>
       </c>
       <c r="AR39" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS39" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT39" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU39" s="3">
         <v>1.0</v>
@@ -6032,25 +6029,25 @@
         <v>0.0</v>
       </c>
       <c r="D40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E40" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F40" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G40" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H40" s="3">
         <v>1.0</v>
       </c>
       <c r="I40" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J40" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K40" s="3">
         <v>-1.0</v>
@@ -6059,40 +6056,40 @@
         <v>-1.0</v>
       </c>
       <c r="M40" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="N40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="O40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="P40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q40" s="3">
         <v>0.0</v>
       </c>
       <c r="R40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="S40" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U40" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V40" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W40" s="3">
         <v>0.0</v>
       </c>
       <c r="X40" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Y40" s="3">
         <v>-1.0</v>
@@ -6101,7 +6098,7 @@
         <v>0.0</v>
       </c>
       <c r="AA40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AB40" s="3">
         <v>-1.0</v>
@@ -6113,10 +6110,10 @@
         <v>1.0</v>
       </c>
       <c r="AE40" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF40" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG40" s="3">
         <v>1.0</v>
@@ -6125,43 +6122,43 @@
         <v>0.0</v>
       </c>
       <c r="AI40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK40" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL40" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AM40" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AN40" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO40" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP40" s="3">
         <v>-1.0</v>
       </c>
       <c r="AQ40" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR40" s="3">
         <v>-1.0</v>
       </c>
       <c r="AS40" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT40" s="3">
         <v>2.0</v>
       </c>
       <c r="AU40" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -6169,49 +6166,49 @@
         <v>40</v>
       </c>
       <c r="B41" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C41" s="3">
         <v>0.0</v>
       </c>
       <c r="D41" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E41" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F41" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G41" s="3">
         <v>0.0</v>
       </c>
       <c r="H41" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41" s="3">
         <v>1.0</v>
       </c>
       <c r="J41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L41" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N41" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P41" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q41" s="3">
         <v>0.0</v>
@@ -6220,16 +6217,16 @@
         <v>-1.0</v>
       </c>
       <c r="S41" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U41" s="3">
         <v>0.0</v>
       </c>
       <c r="V41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W41" s="3">
         <v>0.0</v>
@@ -6241,67 +6238,67 @@
         <v>-1.0</v>
       </c>
       <c r="Z41" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA41" s="3">
         <v>0.0</v>
       </c>
       <c r="AB41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC41" s="3">
         <v>0.0</v>
       </c>
       <c r="AD41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE41" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF41" s="3">
         <v>-1.0</v>
       </c>
       <c r="AG41" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AH41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
       </c>
       <c r="AJ41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK41" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AL41" s="3">
         <v>-1.0</v>
       </c>
       <c r="AM41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AN41" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO41" s="3">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP41" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR41" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS41" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT41" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU41" s="3">
         <v>1.0</v>
@@ -6312,7 +6309,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="C42" s="3">
         <v>0.0</v>
@@ -6324,28 +6321,28 @@
         <v>0.0</v>
       </c>
       <c r="F42" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G42" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I42" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J42" s="3">
         <v>0.0</v>
       </c>
       <c r="K42" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L42" s="3">
         <v>0.0</v>
       </c>
       <c r="M42" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N42" s="3">
         <v>1.0</v>
@@ -6354,43 +6351,43 @@
         <v>-1.0</v>
       </c>
       <c r="P42" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="R42" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S42" s="3">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U42" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="X42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y42" s="3">
         <v>1.0</v>
       </c>
       <c r="Z42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AB42" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC42" s="3">
         <v>0.0</v>
@@ -6402,19 +6399,19 @@
         <v>-1.0</v>
       </c>
       <c r="AF42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG42" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AI42" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ42" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK42" s="3">
         <v>1.0</v>
@@ -6423,7 +6420,7 @@
         <v>1.0</v>
       </c>
       <c r="AM42" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AN42" s="3">
         <v>-1.0</v>
@@ -6432,22 +6429,22 @@
         <v>-1.0</v>
       </c>
       <c r="AP42" s="3">
-        <v>-10.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ42" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR42" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AS42" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AT42" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU42" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -6461,25 +6458,25 @@
         <v>0.0</v>
       </c>
       <c r="D43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F43" s="3">
         <v>-1.0</v>
       </c>
       <c r="G43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I43" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K43" s="3">
         <v>1.0</v>
@@ -6491,67 +6488,67 @@
         <v>2.0</v>
       </c>
       <c r="N43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="V43" s="3">
         <v>1.0</v>
       </c>
       <c r="W43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y43" s="3">
         <v>1.0</v>
       </c>
       <c r="Z43" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AB43" s="3">
         <v>1.0</v>
       </c>
       <c r="AC43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD43" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF43" s="3">
         <v>-1.0</v>
       </c>
       <c r="AG43" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH43" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AI43" s="3">
         <v>1.0</v>
@@ -6560,31 +6557,31 @@
         <v>1.0</v>
       </c>
       <c r="AK43" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM43" s="3">
         <v>1.0</v>
       </c>
       <c r="AN43" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP43" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ43" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR43" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS43" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT43" s="3">
         <v>2.0</v>
@@ -6598,97 +6595,97 @@
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C44" s="3">
         <v>0.0</v>
       </c>
       <c r="D44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="E44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="F44" s="3">
         <v>-1.0</v>
       </c>
       <c r="G44" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H44" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K44" s="3">
         <v>1.0</v>
       </c>
       <c r="L44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M44" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N44" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q44" s="3">
         <v>0.0</v>
       </c>
       <c r="R44" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S44" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="U44" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X44" s="3">
         <v>0.0</v>
       </c>
       <c r="Y44" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Z44" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA44" s="3">
         <v>0.0</v>
       </c>
       <c r="AB44" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC44" s="3">
         <v>0.0</v>
       </c>
       <c r="AD44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF44" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AG44" s="3">
         <v>1.0</v>
@@ -6700,31 +6697,31 @@
         <v>1.0</v>
       </c>
       <c r="AJ44" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AK44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AL44" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AM44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN44" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP44" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ44" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR44" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS44" s="3">
         <v>2.0</v>
@@ -6747,133 +6744,133 @@
         <v>0.0</v>
       </c>
       <c r="D45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="E45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="F45" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G45" s="3">
-        <v>-1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="H45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="I45" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J45" s="3">
         <v>2.0</v>
       </c>
-      <c r="K45" s="4">
-        <v>3.0</v>
+      <c r="K45" s="3">
+        <v>0.0</v>
       </c>
       <c r="L45" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M45" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N45" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O45" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="Q45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="R45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="S45" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T45" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="V45" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="W45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="X45" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="Z45" s="3">
         <v>-1.0</v>
       </c>
       <c r="AA45" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AB45" s="4">
-        <v>3.0</v>
+        <v>-1.0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0.0</v>
       </c>
       <c r="AC45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AD45" s="3">
-        <v>2.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AE45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AF45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AG45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AI45" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ45" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AK45" s="3">
         <v>0.0</v>
       </c>
       <c r="AL45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AM45" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AN45" s="3">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AO45" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP45" s="3">
-        <v>1.0</v>
+        <v>-2.0</v>
       </c>
       <c r="AQ45" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR45" s="3">
         <v>2.0</v>
       </c>
       <c r="AS45" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT45" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AU45" s="3">
         <v>-2.0</v>
@@ -6884,7 +6881,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C46" s="3">
         <v>0.0</v>
@@ -6893,67 +6890,67 @@
         <v>-1.0</v>
       </c>
       <c r="E46" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G46" s="3">
         <v>1.0</v>
       </c>
       <c r="H46" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="I46" s="3">
         <v>0.0</v>
       </c>
       <c r="J46" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L46" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M46" s="3">
         <v>1.0</v>
       </c>
       <c r="N46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O46" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P46" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q46" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R46" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S46" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T46" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="U46" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="V46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W46" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="X46" s="3">
         <v>1.0</v>
       </c>
       <c r="Y46" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Z46" s="3">
         <v>0.0</v>
@@ -6962,7 +6959,7 @@
         <v>1.0</v>
       </c>
       <c r="AB46" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AC46" s="3">
         <v>1.0</v>
@@ -6971,10 +6968,10 @@
         <v>1.0</v>
       </c>
       <c r="AE46" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AF46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AG46" s="3">
         <v>1.0</v>
@@ -6992,31 +6989,31 @@
         <v>1.0</v>
       </c>
       <c r="AL46" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AM46" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AN46" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AO46" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP46" s="3">
         <v>-1.0</v>
       </c>
       <c r="AQ46" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR46" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS46" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AT46" s="3">
-        <v>-10.0</v>
+        <v>1.0</v>
       </c>
       <c r="AU46" s="3">
         <v>0.0</v>
@@ -7033,55 +7030,55 @@
         <v>0.0</v>
       </c>
       <c r="D47" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E47" s="3">
         <v>0.0</v>
       </c>
       <c r="F47" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H47" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K47" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="N47" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O47" s="3">
         <v>0.0</v>
       </c>
       <c r="P47" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q47" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R47" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="S47" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="T47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="U47" s="3">
         <v>0.0</v>
@@ -7090,16 +7087,16 @@
         <v>-1.0</v>
       </c>
       <c r="W47" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X47" s="3">
         <v>-1.0</v>
       </c>
       <c r="Y47" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z47" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AA47" s="3">
         <v>0.0</v>
@@ -7108,25 +7105,25 @@
         <v>0.0</v>
       </c>
       <c r="AC47" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AE47" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF47" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AG47" s="3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AH47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AI47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AJ47" s="3">
         <v>-1.0</v>
@@ -7135,25 +7132,25 @@
         <v>1.0</v>
       </c>
       <c r="AL47" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AM47" s="3">
         <v>1.0</v>
       </c>
       <c r="AN47" s="3">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="AO47" s="3">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AP47" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ47" s="3">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="AR47" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS47" s="3">
         <v>-2.0</v>
@@ -7162,7 +7159,7 @@
         <v>0.0</v>
       </c>
       <c r="AU47" s="3">
-        <v>-10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8BBFA4-FFDD-4C04-9599-27ED49C93351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2E37CE-B071-486A-B8A9-FD7F65BFD683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="AF4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG4" s="3">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR4" s="3">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="AF8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="3">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="AR8" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AS8" s="3">
         <v>1</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2E37CE-B071-486A-B8A9-FD7F65BFD683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D255E467-2780-420A-992E-AA0F87433D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1172,7 +1172,7 @@
         <v>-1</v>
       </c>
       <c r="L5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="3">
         <v>0</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D255E467-2780-420A-992E-AA0F87433D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D61936-A06A-4500-8078-B83761C78072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
   <si>
     <t>Hero</t>
   </si>
@@ -179,15 +179,6 @@
     <t>Soldier 76</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>-0.5</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
     <t>Emre</t>
   </si>
   <si>
@@ -197,27 +188,6 @@
     <t>Mizuki</t>
   </si>
   <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>-0.75</t>
-  </si>
-  <si>
-    <t>-0.25</t>
-  </si>
-  <si>
-    <t>-0.125</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
     <t>Domina</t>
   </si>
 </sst>
@@ -225,7 +195,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -254,6 +224,20 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -281,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -293,6 +277,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -555,7 +545,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -573,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -600,10 +590,10 @@
         <v>23</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>25</v>
@@ -700,8 +690,8 @@
       <c r="I2" s="3">
         <v>-1</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
+      <c r="J2" s="3">
+        <v>-1</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -728,7 +718,7 @@
         <v>-1</v>
       </c>
       <c r="S2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
@@ -754,8 +744,8 @@
       <c r="AA2" s="3">
         <v>-1</v>
       </c>
-      <c r="AB2" s="3" t="s">
-        <v>58</v>
+      <c r="AB2" s="3">
+        <v>1</v>
       </c>
       <c r="AC2" s="3">
         <v>1</v>
@@ -841,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -855,8 +845,8 @@
       <c r="I3" s="3">
         <v>-2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>49</v>
+      <c r="J3" s="3">
+        <v>0</v>
       </c>
       <c r="K3" s="3">
         <v>1</v>
@@ -865,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
         <v>0</v>
@@ -909,11 +899,11 @@
       <c r="AA3" s="3">
         <v>-2</v>
       </c>
-      <c r="AB3" s="3" t="s">
-        <v>56</v>
+      <c r="AB3" s="3">
+        <v>2</v>
       </c>
       <c r="AC3" s="3">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1011,7 +1001,7 @@
         <v>-1</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K4" s="3">
         <v>-1</v>
@@ -1020,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3">
         <v>1</v>
@@ -1038,7 +1028,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4" s="3">
         <v>1</v>
@@ -1064,11 +1054,11 @@
       <c r="AA4" s="3">
         <v>0</v>
       </c>
-      <c r="AB4" s="3" t="s">
-        <v>58</v>
+      <c r="AB4" s="3">
+        <v>2</v>
       </c>
       <c r="AC4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="3">
         <v>1</v>
@@ -1145,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -1175,7 +1165,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3">
         <v>1</v>
@@ -1193,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="S5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="3">
         <v>0</v>
@@ -1220,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD5" s="3">
         <v>1</v>
@@ -1300,7 +1290,7 @@
         <v>-1</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -1320,8 +1310,8 @@
       <c r="I6" s="3">
         <v>-1</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>49</v>
+      <c r="J6" s="3">
+        <v>-1</v>
       </c>
       <c r="K6" s="3">
         <v>2</v>
@@ -1348,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
@@ -1374,8 +1364,8 @@
       <c r="AA6" s="3">
         <v>0</v>
       </c>
-      <c r="AB6" s="3" t="s">
-        <v>58</v>
+      <c r="AB6" s="3">
+        <v>2</v>
       </c>
       <c r="AC6" s="3">
         <v>2</v>
@@ -1485,7 +1475,7 @@
         <v>-1</v>
       </c>
       <c r="M7" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
@@ -1503,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T7" s="3">
         <v>0</v>
@@ -1530,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD7" s="3">
         <v>1</v>
@@ -1630,8 +1620,8 @@
       <c r="I8" s="3">
         <v>-1</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>49</v>
+      <c r="J8" s="3">
+        <v>-1</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -1640,7 +1630,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>1</v>
@@ -1658,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" s="3">
         <v>1</v>
@@ -1684,11 +1674,11 @@
       <c r="AA8" s="3">
         <v>-1</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>55</v>
+      <c r="AB8" s="3">
+        <v>2</v>
       </c>
       <c r="AC8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>1</v>
@@ -1813,7 +1803,7 @@
         <v>2</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
@@ -1839,11 +1829,11 @@
       <c r="AA9" s="3">
         <v>0</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>56</v>
+      <c r="AB9" s="3">
+        <v>1</v>
       </c>
       <c r="AC9" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD9" s="3">
         <v>1</v>
@@ -1914,7 +1904,7 @@
     </row>
     <row r="10" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1923,16 +1913,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3">
         <v>-1</v>
       </c>
       <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>1</v>
@@ -1950,19 +1940,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="3">
         <v>1</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>48</v>
+      <c r="P10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3">
         <v>1</v>
@@ -1976,8 +1966,8 @@
       <c r="U10" s="3">
         <v>1</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>49</v>
+      <c r="V10" s="3">
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>1</v>
@@ -1985,20 +1975,20 @@
       <c r="X10" s="3">
         <v>-1</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>49</v>
+      <c r="Y10" s="3">
+        <v>-1</v>
       </c>
       <c r="Z10" s="3">
         <v>1</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>49</v>
+        <v>-1</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -2007,10 +1997,10 @@
         <v>1</v>
       </c>
       <c r="AF10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0</v>
       </c>
       <c r="AH10" s="3">
         <v>1</v>
@@ -2021,35 +2011,35 @@
       <c r="AJ10" s="3">
         <v>0</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>48</v>
+      <c r="AK10" s="3">
+        <v>0</v>
       </c>
       <c r="AL10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ10" s="3" t="s">
-        <v>49</v>
+        <v>-1</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="3">
+        <v>0</v>
       </c>
       <c r="AR10" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AS10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AT10" s="3" t="s">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="AS10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="3">
+        <v>2</v>
       </c>
       <c r="AU10" s="3">
         <v>0</v>
@@ -2060,8 +2050,8 @@
       <c r="AW10" s="3">
         <v>-1</v>
       </c>
-      <c r="AX10" s="3" t="s">
-        <v>48</v>
+      <c r="AX10" s="3">
+        <v>0</v>
       </c>
       <c r="AY10" s="3">
         <v>0</v>
@@ -2075,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -2096,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2105,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="M11" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N11" s="3">
         <v>-1</v>
@@ -2123,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T11" s="3">
         <v>0</v>
@@ -2250,8 +2240,8 @@
       <c r="I12" s="3">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>48</v>
+      <c r="J12" s="3">
+        <v>1</v>
       </c>
       <c r="K12" s="3">
         <v>1</v>
@@ -2260,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N12" s="3">
         <v>-1</v>
@@ -2278,7 +2268,7 @@
         <v>-1</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
@@ -2305,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="AB12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" s="3">
         <v>1</v>
@@ -2379,25 +2369,25 @@
     </row>
     <row r="13" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B13" s="3">
         <v>-1</v>
       </c>
       <c r="C13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3">
         <v>0</v>
@@ -2406,13 +2396,13 @@
         <v>-1</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -2421,25 +2411,25 @@
         <v>1</v>
       </c>
       <c r="O13" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P13" s="3">
         <v>-1</v>
       </c>
       <c r="Q13" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="R13" s="3">
         <v>0</v>
       </c>
       <c r="S13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="3">
         <v>2</v>
@@ -2448,25 +2438,25 @@
         <v>-1</v>
       </c>
       <c r="X13" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3">
         <v>0</v>
       </c>
       <c r="AA13" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="3">
         <v>0</v>
@@ -2475,13 +2465,13 @@
         <v>1</v>
       </c>
       <c r="AG13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="3">
         <v>0</v>
       </c>
       <c r="AI13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ13" s="3">
         <v>0</v>
@@ -2490,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="AL13" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM13" s="3">
         <v>0</v>
@@ -2505,31 +2495,31 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS13" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT13" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV13" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AW13" s="3">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AX13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY13" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2561,7 +2551,7 @@
         <v>-1</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2614,11 +2604,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>58</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -2695,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -2769,11 +2759,11 @@
       <c r="AA15" s="3">
         <v>-1</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>58</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD15" s="3">
         <v>-1</v>
@@ -2870,8 +2860,8 @@
       <c r="I16" s="3">
         <v>-1</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>48</v>
+      <c r="J16" s="3">
+        <v>0</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
@@ -2924,8 +2914,8 @@
       <c r="AA16" s="3">
         <v>1</v>
       </c>
-      <c r="AB16" s="3" t="s">
-        <v>55</v>
+      <c r="AB16" s="3">
+        <v>0</v>
       </c>
       <c r="AC16" s="3">
         <v>0</v>
@@ -3025,8 +3015,8 @@
       <c r="I17" s="3">
         <v>-1</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
+      <c r="J17" s="3">
+        <v>1</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -3035,7 +3025,7 @@
         <v>-1</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N17" s="3">
         <v>-1</v>
@@ -3053,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
@@ -3083,7 +3073,7 @@
         <v>-1</v>
       </c>
       <c r="AC17" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -3160,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D18" s="3">
         <v>-1</v>
@@ -3180,8 +3170,8 @@
       <c r="I18" s="3">
         <v>-1</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>49</v>
+      <c r="J18" s="3">
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-1</v>
@@ -3235,10 +3225,10 @@
         <v>-1</v>
       </c>
       <c r="AB18" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -3309,43 +3299,43 @@
     </row>
     <row r="19" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C19" s="3">
         <v>0</v>
       </c>
       <c r="D19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
       </c>
       <c r="M19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N19" s="3">
         <v>0</v>
@@ -3369,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="3">
         <v>0</v>
@@ -3390,22 +3380,22 @@
         <v>0</v>
       </c>
       <c r="AB19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" s="3">
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" s="3">
         <v>0</v>
@@ -3417,16 +3407,16 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" s="3">
         <v>0</v>
       </c>
       <c r="AM19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO19" s="3">
         <v>1</v>
@@ -3441,25 +3431,25 @@
         <v>0</v>
       </c>
       <c r="AS19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV19" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,8 +3480,8 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>49</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -3500,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -3545,7 +3535,7 @@
         <v>-1</v>
       </c>
       <c r="AB20" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
@@ -3625,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="C21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3">
         <v>-1</v>
@@ -3655,7 +3645,7 @@
         <v>-1</v>
       </c>
       <c r="M21" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3">
         <v>-1</v>
@@ -3673,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T21" s="3">
         <v>0</v>
@@ -3699,11 +3689,11 @@
       <c r="AA21" s="3">
         <v>2</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>55</v>
+      <c r="AB21" s="3">
+        <v>-1</v>
       </c>
       <c r="AC21" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AD21" s="3">
         <v>1</v>
@@ -3855,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="3">
         <v>1</v>
@@ -3955,8 +3945,8 @@
       <c r="I23" s="3">
         <v>-1</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>49</v>
+      <c r="J23" s="3">
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>1</v>
@@ -3965,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="3">
         <v>1</v>
@@ -4010,7 +4000,7 @@
         <v>2</v>
       </c>
       <c r="AB23" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC23" s="3">
         <v>-1</v>
@@ -4090,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -4110,8 +4100,8 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>50</v>
+      <c r="J24" s="3">
+        <v>1</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -4120,7 +4110,7 @@
         <v>-1</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -4138,7 +4128,7 @@
         <v>-1</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -4164,11 +4154,11 @@
       <c r="AA24" s="3">
         <v>2</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>49</v>
+      <c r="AB24" s="3">
+        <v>-1</v>
       </c>
       <c r="AC24" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>-1</v>
@@ -4245,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -4275,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="3">
         <v>1</v>
@@ -4321,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="AC25" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD25" s="3">
         <v>-1</v>
@@ -4473,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
@@ -4574,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -4601,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
@@ -4627,11 +4617,11 @@
       <c r="AA27" s="3">
         <v>1</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>58</v>
+      <c r="AB27" s="3">
+        <v>0</v>
       </c>
       <c r="AC27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" s="3">
         <v>1</v>
@@ -4702,109 +4692,109 @@
     </row>
     <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-1</v>
       </c>
       <c r="C28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>56</v>
+        <v>-1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-1</v>
       </c>
       <c r="G28" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
       </c>
       <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>55</v>
+        <v>-1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-1</v>
       </c>
       <c r="N28" s="3">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>-1</v>
       </c>
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>50</v>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="S28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
       </c>
       <c r="U28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
       </c>
       <c r="Y28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>54</v>
+        <v>-1</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>1</v>
       </c>
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-      <c r="AC28" s="3" t="s">
-        <v>58</v>
+      <c r="AC28" s="3">
+        <v>0</v>
       </c>
       <c r="AD28" s="3">
         <v>-1</v>
       </c>
-      <c r="AE28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF28" s="3" t="s">
-        <v>58</v>
+      <c r="AE28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
       </c>
       <c r="AG28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI28" s="3" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
       </c>
       <c r="AJ28" s="3">
         <v>0</v>
@@ -4812,82 +4802,82 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
-      <c r="AL28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AN28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AR28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AS28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AT28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AU28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AV28" s="3" t="s">
-        <v>56</v>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="3">
+        <v>0</v>
       </c>
       <c r="AW28" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AX28" s="3" t="s">
-        <v>58</v>
+        <v>-2</v>
+      </c>
+      <c r="AX28" s="3">
+        <v>1</v>
       </c>
       <c r="AY28" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>24</v>
+      <c r="A29" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B29" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3">
         <v>0</v>
       </c>
       <c r="D29" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>-1</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3">
         <v>-1</v>
@@ -4899,25 +4889,25 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V29" s="3">
         <v>-1</v>
@@ -4926,40 +4916,40 @@
         <v>1</v>
       </c>
       <c r="X29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y29" s="3">
         <v>1</v>
       </c>
       <c r="Z29" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD29" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE29" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ29" s="3">
         <v>0</v>
@@ -4971,40 +4961,40 @@
         <v>0</v>
       </c>
       <c r="AM29" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN29" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29" s="3">
         <v>-1</v>
       </c>
       <c r="AQ29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR29" s="3">
         <v>0</v>
       </c>
       <c r="AS29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT29" s="3">
         <v>0</v>
       </c>
       <c r="AU29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW29" s="3">
         <v>-2</v>
       </c>
       <c r="AX29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY29" s="3">
         <v>-1</v>
@@ -5039,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -5048,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N30" s="3">
         <v>1</v>
@@ -5066,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="3">
         <v>0</v>
@@ -5092,11 +5082,11 @@
       <c r="AA30" s="3">
         <v>-1</v>
       </c>
-      <c r="AB30" s="3" t="s">
-        <v>58</v>
+      <c r="AB30" s="3">
+        <v>0</v>
       </c>
       <c r="AC30" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD30" s="3">
         <v>-1</v>
@@ -5173,7 +5163,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D31" s="3">
         <v>0</v>
@@ -5247,11 +5237,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-      <c r="AB31" s="3" t="s">
-        <v>56</v>
+      <c r="AB31" s="3">
+        <v>0</v>
       </c>
       <c r="AC31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" s="3">
         <v>1</v>
@@ -5358,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-1</v>
@@ -5376,7 +5366,7 @@
         <v>-1</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
@@ -5402,11 +5392,11 @@
       <c r="AA32" s="3">
         <v>1</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>56</v>
+      <c r="AB32" s="3">
+        <v>-1</v>
       </c>
       <c r="AC32" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AD32" s="3">
         <v>1</v>
@@ -5503,8 +5493,8 @@
       <c r="I33" s="3">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>48</v>
+      <c r="J33" s="3">
+        <v>1</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -5513,7 +5503,7 @@
         <v>-1</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N33" s="3">
         <v>-1</v>
@@ -5531,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T33" s="3">
         <v>-1</v>
@@ -5557,11 +5547,11 @@
       <c r="AA33" s="3">
         <v>-1</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>58</v>
+      <c r="AB33" s="3">
+        <v>-1</v>
       </c>
       <c r="AC33" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD33" s="3">
         <v>-1</v>
@@ -5638,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3">
         <v>-1</v>
@@ -5668,7 +5658,7 @@
         <v>-2</v>
       </c>
       <c r="M34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="3">
         <v>-2</v>
@@ -5793,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3">
         <v>-1</v>
@@ -5813,8 +5803,8 @@
       <c r="I35" s="3">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>50</v>
+      <c r="J35" s="3">
+        <v>1</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -5841,7 +5831,7 @@
         <v>-1</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -5867,11 +5857,11 @@
       <c r="AA35" s="3">
         <v>-1</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>58</v>
+      <c r="AB35" s="3">
+        <v>-1</v>
       </c>
       <c r="AC35" s="3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AD35" s="3">
         <v>0</v>
@@ -5969,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
@@ -5978,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="3">
         <v>1</v>
@@ -5996,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="3">
         <v>0</v>
@@ -6022,8 +6012,8 @@
       <c r="AA36" s="3">
         <v>-1</v>
       </c>
-      <c r="AB36" s="3" t="s">
-        <v>55</v>
+      <c r="AB36" s="3">
+        <v>0</v>
       </c>
       <c r="AC36" s="3">
         <v>0</v>
@@ -6133,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" s="3">
         <v>1</v>
@@ -6177,8 +6167,8 @@
       <c r="AA37" s="3">
         <v>-1</v>
       </c>
-      <c r="AB37" s="3" t="s">
-        <v>49</v>
+      <c r="AB37" s="3">
+        <v>0</v>
       </c>
       <c r="AC37" s="3">
         <v>0</v>
@@ -6278,8 +6268,8 @@
       <c r="I38" s="3">
         <v>-1</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>49</v>
+      <c r="J38" s="3">
+        <v>-1</v>
       </c>
       <c r="K38" s="3">
         <v>-1</v>
@@ -6288,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3">
         <v>0</v>
@@ -6306,7 +6296,7 @@
         <v>2</v>
       </c>
       <c r="S38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
@@ -6332,11 +6322,11 @@
       <c r="AA38" s="3">
         <v>1</v>
       </c>
-      <c r="AB38" s="3" t="s">
-        <v>58</v>
+      <c r="AB38" s="3">
+        <v>1</v>
       </c>
       <c r="AC38" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD38" s="3">
         <v>1</v>
@@ -6434,7 +6424,7 @@
         <v>-1</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -6461,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
@@ -6488,10 +6478,10 @@
         <v>-1</v>
       </c>
       <c r="AB39" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC39" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD39" s="3">
         <v>0</v>
@@ -6588,8 +6578,8 @@
       <c r="I40" s="3">
         <v>-2</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>48</v>
+      <c r="J40" s="3">
+        <v>2</v>
       </c>
       <c r="K40" s="3">
         <v>2</v>
@@ -6598,7 +6588,7 @@
         <v>2</v>
       </c>
       <c r="M40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N40" s="3">
         <v>1</v>
@@ -6616,7 +6606,7 @@
         <v>-1</v>
       </c>
       <c r="S40" s="3">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="T40" s="3">
         <v>-1</v>
@@ -6642,11 +6632,11 @@
       <c r="AA40" s="3">
         <v>-2</v>
       </c>
-      <c r="AB40" s="3" t="s">
-        <v>60</v>
+      <c r="AB40" s="3">
+        <v>2</v>
       </c>
       <c r="AC40" s="3">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AD40" s="3">
         <v>1</v>
@@ -6743,8 +6733,8 @@
       <c r="I41" s="3">
         <v>1</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>48</v>
+      <c r="J41" s="3">
+        <v>1</v>
       </c>
       <c r="K41" s="3">
         <v>-2</v>
@@ -6753,7 +6743,7 @@
         <v>-1</v>
       </c>
       <c r="M41" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -6771,7 +6761,7 @@
         <v>-1</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
@@ -6797,11 +6787,11 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>56</v>
+      <c r="AB41" s="3">
+        <v>-1</v>
       </c>
       <c r="AC41" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -6908,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -6952,8 +6942,8 @@
       <c r="AA42" s="3">
         <v>-1</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>60</v>
+      <c r="AB42" s="3">
+        <v>1</v>
       </c>
       <c r="AC42" s="3">
         <v>1</v>
@@ -7053,8 +7043,8 @@
       <c r="I43" s="3">
         <v>-2</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>49</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>1</v>
@@ -7063,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -7107,11 +7097,11 @@
       <c r="AA43" s="3">
         <v>-2</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>56</v>
+      <c r="AB43" s="3">
+        <v>2</v>
       </c>
       <c r="AC43" s="3">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -7208,8 +7198,8 @@
       <c r="I44" s="3">
         <v>2</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>50</v>
+      <c r="J44" s="3">
+        <v>2</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -7218,7 +7208,7 @@
         <v>-1</v>
       </c>
       <c r="M44" s="3">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N44" s="3">
         <v>-1</v>
@@ -7262,11 +7252,11 @@
       <c r="AA44" s="3">
         <v>-1</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>58</v>
+      <c r="AB44" s="3">
+        <v>-1</v>
       </c>
       <c r="AC44" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -7363,8 +7353,8 @@
       <c r="I45" s="3">
         <v>1</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>49</v>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>-1</v>
@@ -7391,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -7417,11 +7407,11 @@
       <c r="AA45" s="3">
         <v>-1</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>57</v>
+      <c r="AB45" s="3">
+        <v>-1</v>
       </c>
       <c r="AC45" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>-1</v>
@@ -7498,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -7519,7 +7509,7 @@
         <v>-1</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -7528,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -7546,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
@@ -7573,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="AB46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD46" s="3">
         <v>0</v>
@@ -7653,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -7673,8 +7663,8 @@
       <c r="I47" s="3">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>50</v>
+      <c r="J47" s="3">
+        <v>1</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -7683,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -7701,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
@@ -7727,11 +7717,11 @@
       <c r="AA47" s="3">
         <v>1</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>55</v>
+      <c r="AB47" s="3">
+        <v>1</v>
       </c>
       <c r="AC47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="3">
         <v>-1</v>
@@ -7808,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -7838,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="M48" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -7856,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -7883,10 +7873,10 @@
         <v>0</v>
       </c>
       <c r="AB48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD48" s="3">
         <v>-1</v>
@@ -7993,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -8011,7 +8001,7 @@
         <v>-2</v>
       </c>
       <c r="S49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="3">
         <v>-2</v>
@@ -8038,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="3">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AC49" s="3">
         <v>-2</v>
@@ -8118,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="C50" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D50" s="3">
         <v>-1</v>
@@ -8148,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="3">
         <v>-1</v>
@@ -8166,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="S50" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
@@ -8192,11 +8182,11 @@
       <c r="AA50" s="3">
         <v>1</v>
       </c>
-      <c r="AB50" s="3" t="s">
-        <v>56</v>
+      <c r="AB50" s="3">
+        <v>-1</v>
       </c>
       <c r="AC50" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD50" s="3">
         <v>0</v>
@@ -8273,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D51" s="3">
         <v>0</v>
@@ -8293,8 +8283,8 @@
       <c r="I51" s="3">
         <v>-1</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>49</v>
+      <c r="J51" s="3">
+        <v>-1</v>
       </c>
       <c r="K51" s="3">
         <v>-1</v>
@@ -8303,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N51" s="3">
         <v>-1</v>
@@ -8321,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
@@ -8348,10 +8338,10 @@
         <v>-1</v>
       </c>
       <c r="AB51" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD51" s="3">
         <v>-1</v>
@@ -8420,7 +8410,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
     <row r="53" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="55" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D61936-A06A-4500-8078-B83761C78072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3C42C-8E4C-49C2-8B48-6529BADD0329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Roadhog</t>
+  </si>
+  <si>
+    <t>Sierra</t>
   </si>
   <si>
     <t>Sigma</t>
@@ -603,6 +606,9 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -714,48 +720,51 @@
         <v>-1</v>
       </c>
       <c r="AK2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM2" s="2">
         <v>0</v>
       </c>
       <c r="AN2" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ2" s="2">
         <v>0</v>
       </c>
       <c r="AR2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ2" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -872,19 +881,19 @@
         <v>0</v>
       </c>
       <c r="AL3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO3" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ3" s="2">
         <v>0</v>
@@ -896,21 +905,24 @@
         <v>0</v>
       </c>
       <c r="AT3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" s="2">
         <v>0</v>
       </c>
       <c r="AW3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX3" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ3" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1024,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="AK4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM4" s="2">
         <v>0</v>
@@ -1042,30 +1054,33 @@
         <v>0</v>
       </c>
       <c r="AQ4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS4" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AT4" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU4" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AV4" s="2">
         <v>-1</v>
       </c>
       <c r="AW4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX4" s="2">
         <v>0</v>
       </c>
       <c r="AY4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1179,19 +1194,19 @@
         <v>1</v>
       </c>
       <c r="AK5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="2">
         <v>-1</v>
@@ -1200,27 +1215,30 @@
         <v>-1</v>
       </c>
       <c r="AR5" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AS5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU5" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW5" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1334,48 +1352,51 @@
         <v>2</v>
       </c>
       <c r="AK6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO6" s="2">
         <v>1</v>
       </c>
       <c r="AP6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR6" s="2">
         <v>1</v>
       </c>
       <c r="AS6" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT6" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW6" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AX6" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AY6" s="2">
+        <v>2</v>
+      </c>
+      <c r="AZ6" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1495,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="AM7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" s="2">
         <v>0</v>
       </c>
       <c r="AP7" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR7" s="2">
         <v>1</v>
@@ -1516,21 +1537,24 @@
         <v>1</v>
       </c>
       <c r="AT7" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" s="2">
         <v>1</v>
       </c>
       <c r="AX7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1643,49 +1667,52 @@
       <c r="AJ8" s="2">
         <v>-1</v>
       </c>
-      <c r="AK8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="2">
+      <c r="AK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
         <v>0</v>
       </c>
       <c r="AM8" s="2">
         <v>0</v>
       </c>
       <c r="AN8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="2">
         <v>-1</v>
       </c>
       <c r="AS8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX8" s="2">
         <v>-1</v>
       </c>
       <c r="AY8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ8" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1805,42 +1832,45 @@
         <v>0</v>
       </c>
       <c r="AM9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR9" s="2">
         <v>1</v>
       </c>
       <c r="AS9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="2">
         <v>-1</v>
       </c>
       <c r="AX9" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AY9" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AZ9" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1957,22 +1987,22 @@
         <v>0</v>
       </c>
       <c r="AL10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP10" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AR10" s="2">
         <v>-1</v>
@@ -1981,21 +2011,24 @@
         <v>-1</v>
       </c>
       <c r="AT10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AV10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -2118,25 +2151,25 @@
         <v>0</v>
       </c>
       <c r="AN11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AR11" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS11" s="2">
         <v>0</v>
       </c>
       <c r="AT11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" s="2">
         <v>1</v>
@@ -2145,12 +2178,15 @@
         <v>1</v>
       </c>
       <c r="AW11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2264,13 +2300,13 @@
         <v>0</v>
       </c>
       <c r="AK12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="2">
         <v>0</v>
@@ -2279,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="AP12" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR12" s="2">
         <v>0</v>
@@ -2294,10 +2330,10 @@
         <v>0</v>
       </c>
       <c r="AU12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" s="2">
         <v>0</v>
@@ -2306,6 +2342,9 @@
         <v>0</v>
       </c>
       <c r="AY12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2422,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="AL13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN13" s="2">
         <v>0</v>
@@ -2437,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="2">
         <v>-1</v>
@@ -2446,7 +2485,7 @@
         <v>-1</v>
       </c>
       <c r="AT13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU13" s="2">
         <v>0</v>
@@ -2458,9 +2497,12 @@
         <v>0</v>
       </c>
       <c r="AX13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2574,48 +2616,51 @@
         <v>-1</v>
       </c>
       <c r="AK14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" s="2">
         <v>0</v>
       </c>
       <c r="AR14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS14" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV14" s="2">
         <v>-1</v>
       </c>
       <c r="AW14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2732,45 +2777,48 @@
         <v>0</v>
       </c>
       <c r="AL15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" s="2">
         <v>1</v>
       </c>
       <c r="AN15" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP15" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU15" s="2">
         <v>-1</v>
       </c>
       <c r="AV15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX15" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ15" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -2884,48 +2932,51 @@
         <v>1</v>
       </c>
       <c r="AK16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN16" s="2">
         <v>0</v>
       </c>
       <c r="AO16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" s="2">
         <v>1</v>
       </c>
       <c r="AQ16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS16" s="2">
         <v>-2</v>
       </c>
       <c r="AT16" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU16" s="2">
         <v>0</v>
       </c>
       <c r="AV16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW16" s="2">
         <v>-1</v>
       </c>
       <c r="AX16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3039,48 +3090,51 @@
         <v>0</v>
       </c>
       <c r="AK17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO17" s="2">
         <v>0</v>
       </c>
       <c r="AP17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AR17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS17" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV17" s="2">
         <v>-1</v>
       </c>
       <c r="AW17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3194,48 +3248,51 @@
         <v>-1</v>
       </c>
       <c r="AK18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ18" s="2">
         <v>-1</v>
       </c>
       <c r="AR18" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS18" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT18" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV18" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AW18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -3349,48 +3406,51 @@
         <v>-1</v>
       </c>
       <c r="AK19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" s="2">
         <v>0</v>
       </c>
       <c r="AO19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ19" s="2">
         <v>1</v>
       </c>
       <c r="AR19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS19" s="2">
         <v>0</v>
       </c>
       <c r="AT19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" s="2">
         <v>0</v>
       </c>
       <c r="AW19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" s="2">
         <v>1</v>
       </c>
       <c r="AY19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3507,16 +3567,16 @@
         <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM20" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AN20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP20" s="2">
         <v>0</v>
@@ -3531,21 +3591,24 @@
         <v>0</v>
       </c>
       <c r="AT20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV20" s="2">
         <v>0</v>
       </c>
       <c r="AW20" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AX20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ20" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -3662,45 +3725,48 @@
         <v>0</v>
       </c>
       <c r="AL21" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM21" s="2">
         <v>-1</v>
       </c>
       <c r="AN21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP21" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT21" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW21" s="2">
         <v>1</v>
       </c>
       <c r="AX21" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ21" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -3817,45 +3883,48 @@
         <v>0</v>
       </c>
       <c r="AL22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO22" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22" s="2">
         <v>0</v>
       </c>
       <c r="AS22" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AT22" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AU22" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AV22" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX22" s="2">
         <v>0</v>
       </c>
       <c r="AY22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3972,45 +4041,48 @@
         <v>0</v>
       </c>
       <c r="AL23" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AN23" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AO23" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AP23" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ23" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT23" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AU23" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW23" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AX23" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ23" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4130,22 +4202,22 @@
         <v>0</v>
       </c>
       <c r="AM24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ24" s="2">
         <v>-1</v>
       </c>
       <c r="AR24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS24" s="2">
         <v>0</v>
@@ -4160,12 +4232,15 @@
         <v>0</v>
       </c>
       <c r="AW24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX24" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ24" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4279,48 +4354,51 @@
         <v>1</v>
       </c>
       <c r="AK25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" s="2">
         <v>0</v>
       </c>
       <c r="AN25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="2">
         <v>1</v>
       </c>
       <c r="AP25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR25" s="2">
         <v>1</v>
       </c>
       <c r="AS25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" s="2">
         <v>0</v>
       </c>
       <c r="AU25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX25" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ25" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4434,16 +4512,16 @@
         <v>1</v>
       </c>
       <c r="AK26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26" s="2">
         <v>0</v>
@@ -4455,27 +4533,30 @@
         <v>0</v>
       </c>
       <c r="AR26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS26" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU26" s="2">
         <v>0</v>
       </c>
       <c r="AV26" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX26" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ26" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4589,19 +4670,19 @@
         <v>1</v>
       </c>
       <c r="AK27" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="2">
         <v>1</v>
       </c>
       <c r="AO27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27" s="2">
         <v>0</v>
@@ -4610,13 +4691,13 @@
         <v>0</v>
       </c>
       <c r="AR27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS27" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT27" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU27" s="2">
         <v>0</v>
@@ -4625,12 +4706,15 @@
         <v>0</v>
       </c>
       <c r="AW27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX27" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AY27" s="2">
+        <v>2</v>
+      </c>
+      <c r="AZ27" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4747,45 +4831,48 @@
         <v>0</v>
       </c>
       <c r="AL28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="2">
         <v>1</v>
       </c>
       <c r="AN28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO28" s="2">
         <v>-1</v>
       </c>
       <c r="AP28" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ28" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AR28" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT28" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV28" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AW28" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AX28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ28" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4902,45 +4989,48 @@
         <v>0</v>
       </c>
       <c r="AL29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN29" s="2">
         <v>1</v>
       </c>
       <c r="AO29" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP29" s="2">
         <v>-1</v>
       </c>
       <c r="AQ29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS29" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX29" s="2">
         <v>1</v>
       </c>
       <c r="AY29" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ29" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -5054,37 +5144,37 @@
         <v>0</v>
       </c>
       <c r="AK30" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL30" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AM30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP30" s="2">
         <v>0</v>
       </c>
       <c r="AQ30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR30" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS30" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AT30" s="2">
         <v>-1</v>
       </c>
       <c r="AU30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV30" s="2">
         <v>0</v>
@@ -5093,9 +5183,12 @@
         <v>0</v>
       </c>
       <c r="AX30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ30" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5212,10 +5305,10 @@
         <v>0</v>
       </c>
       <c r="AL31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN31" s="2">
         <v>0</v>
@@ -5224,13 +5317,13 @@
         <v>0</v>
       </c>
       <c r="AP31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS31" s="2">
         <v>0</v>
@@ -5239,18 +5332,21 @@
         <v>0</v>
       </c>
       <c r="AU31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV31" s="2">
         <v>1</v>
       </c>
       <c r="AW31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX31" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ31" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5367,34 +5463,34 @@
         <v>0</v>
       </c>
       <c r="AL32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO32" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ32" s="2">
         <v>0</v>
       </c>
       <c r="AR32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" s="2">
         <v>1</v>
       </c>
       <c r="AT32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV32" s="2">
         <v>-1</v>
@@ -5403,9 +5499,12 @@
         <v>-1</v>
       </c>
       <c r="AX32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5519,48 +5618,51 @@
         <v>0</v>
       </c>
       <c r="AK33" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AM33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" s="2">
         <v>0</v>
       </c>
       <c r="AO33" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP33" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV33" s="2">
         <v>0</v>
       </c>
       <c r="AW33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ33" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5683,39 +5785,42 @@
         <v>0</v>
       </c>
       <c r="AN34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO34" s="2">
         <v>-1</v>
       </c>
       <c r="AP34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR34" s="2">
         <v>-1</v>
       </c>
       <c r="AS34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV34" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AW34" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AX34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ34" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5832,10 +5937,10 @@
         <v>0</v>
       </c>
       <c r="AL35" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM35" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AN35" s="2">
         <v>0</v>
@@ -5844,33 +5949,36 @@
         <v>0</v>
       </c>
       <c r="AP35" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ35" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT35" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW35" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ35" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5984,48 +6092,51 @@
         <v>0</v>
       </c>
       <c r="AK36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL36" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AM36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN36" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO36" s="2">
         <v>-1</v>
       </c>
       <c r="AP36" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AQ36" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS36" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT36" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW36" s="2">
         <v>0</v>
       </c>
       <c r="AX36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY36" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ36" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6034,19 +6145,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
@@ -6055,58 +6166,58 @@
         <v>0</v>
       </c>
       <c r="I37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
       </c>
       <c r="N37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2">
         <v>0</v>
       </c>
       <c r="P37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" s="2">
         <v>0</v>
       </c>
       <c r="V37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="2">
         <v>0</v>
       </c>
       <c r="Z37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="2">
         <v>0</v>
@@ -6118,25 +6229,25 @@
         <v>0</v>
       </c>
       <c r="AD37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" s="2">
         <v>0</v>
@@ -6145,16 +6256,16 @@
         <v>0</v>
       </c>
       <c r="AM37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AO37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ37" s="2">
         <v>0</v>
@@ -6166,21 +6277,24 @@
         <v>0</v>
       </c>
       <c r="AT37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU37" s="2">
         <v>0</v>
       </c>
       <c r="AV37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AY37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6189,82 +6303,82 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2">
         <v>-1</v>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J38" s="2">
         <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S38" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="2">
         <v>0</v>
       </c>
       <c r="V38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W38" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X38" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y38" s="2">
         <v>0</v>
       </c>
       <c r="Z38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="2">
         <v>0</v>
@@ -6273,70 +6387,73 @@
         <v>0</v>
       </c>
       <c r="AD38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG38" s="2">
         <v>-1</v>
       </c>
       <c r="AH38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI38" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AJ38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="2">
         <v>0</v>
       </c>
       <c r="AL38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AP38" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV38" s="2">
         <v>0</v>
       </c>
       <c r="AW38" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY38" s="2">
-        <v>-1</v>
+        <v>-2</v>
+      </c>
+      <c r="AZ38" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -6347,58 +6464,58 @@
         <v>0</v>
       </c>
       <c r="C39" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D39" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
       </c>
       <c r="I39" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2">
         <v>-1</v>
       </c>
       <c r="P39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="2">
         <v>-1</v>
       </c>
       <c r="S39" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="T39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U39" s="2">
         <v>0</v>
@@ -6407,31 +6524,31 @@
         <v>0</v>
       </c>
       <c r="W39" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="X39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AB39" s="2">
         <v>0</v>
       </c>
       <c r="AC39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF39" s="2">
         <v>-1</v>
@@ -6443,22 +6560,22 @@
         <v>1</v>
       </c>
       <c r="AI39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AK39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL39" s="2">
         <v>0</v>
       </c>
       <c r="AM39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO39" s="2">
         <v>0</v>
@@ -6467,30 +6584,33 @@
         <v>0</v>
       </c>
       <c r="AQ39" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AR39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS39" s="2">
         <v>-1</v>
       </c>
       <c r="AT39" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AU39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX39" s="2">
         <v>1</v>
       </c>
       <c r="AY39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -6499,19 +6619,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>-2</v>
@@ -6520,31 +6640,31 @@
         <v>1</v>
       </c>
       <c r="I40" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
       </c>
       <c r="K40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2">
         <v>1</v>
       </c>
       <c r="O40" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="P40" s="2">
         <v>0</v>
       </c>
       <c r="Q40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R40" s="2">
         <v>-1</v>
@@ -6553,61 +6673,61 @@
         <v>2</v>
       </c>
       <c r="T40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X40" s="2">
         <v>2</v>
       </c>
       <c r="Y40" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Z40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AA40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AB40" s="2">
         <v>0</v>
       </c>
       <c r="AC40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD40" s="2">
         <v>1</v>
       </c>
       <c r="AE40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH40" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AI40" s="2">
         <v>0</v>
       </c>
       <c r="AJ40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AK40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM40" s="2">
         <v>0</v>
@@ -6616,37 +6736,40 @@
         <v>0</v>
       </c>
       <c r="AO40" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP40" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ40" s="2">
         <v>0</v>
       </c>
       <c r="AR40" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AS40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT40" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AU40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV40" s="2">
         <v>0</v>
       </c>
       <c r="AW40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY40" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AZ40" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -6654,58 +6777,58 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" s="2">
         <v>0</v>
       </c>
       <c r="Q41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T41" s="2">
         <v>0</v>
@@ -6714,58 +6837,58 @@
         <v>-2</v>
       </c>
       <c r="V41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AB41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AG41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AI41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AN41" s="2">
         <v>0</v>
@@ -6777,31 +6900,34 @@
         <v>-1</v>
       </c>
       <c r="AQ41" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AR41" s="2">
         <v>0</v>
       </c>
       <c r="AS41" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV41" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AW41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX41" s="2">
         <v>0</v>
       </c>
       <c r="AY41" s="2">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -6812,52 +6938,52 @@
         <v>0</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" s="2">
         <v>-1</v>
@@ -6866,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V42" s="2">
         <v>-1</v>
@@ -6875,19 +7001,19 @@
         <v>0</v>
       </c>
       <c r="X42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Z42" s="2">
         <v>1</v>
       </c>
       <c r="AA42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC42" s="2">
         <v>0</v>
@@ -6899,31 +7025,31 @@
         <v>1</v>
       </c>
       <c r="AF42" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AG42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ42" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK42" s="2">
         <v>0</v>
       </c>
       <c r="AL42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM42" s="2">
         <v>0</v>
       </c>
       <c r="AN42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="2">
         <v>0</v>
@@ -6932,31 +7058,34 @@
         <v>0</v>
       </c>
       <c r="AQ42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS42" s="2">
         <v>0</v>
       </c>
       <c r="AT42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU42" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AV42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AX42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY42" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -6964,7 +7093,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -6976,43 +7105,43 @@
         <v>1</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2">
         <v>1</v>
       </c>
       <c r="M43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2">
         <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q43" s="2">
         <v>0</v>
       </c>
       <c r="R43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S43" s="2">
         <v>-1</v>
@@ -7024,19 +7153,19 @@
         <v>-1</v>
       </c>
       <c r="V43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W43" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="X43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y43" s="2">
         <v>-1</v>
       </c>
       <c r="Z43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA43" s="2">
         <v>-1</v>
@@ -7045,16 +7174,16 @@
         <v>1</v>
       </c>
       <c r="AC43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AG43" s="2">
         <v>0</v>
@@ -7066,25 +7195,25 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AK43" s="2">
         <v>0</v>
       </c>
       <c r="AL43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN43" s="2">
         <v>0</v>
       </c>
       <c r="AO43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP43" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ43" s="2">
         <v>0</v>
@@ -7093,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="AS43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT43" s="2">
         <v>0</v>
@@ -7102,16 +7231,19 @@
         <v>0</v>
       </c>
       <c r="AV43" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX43" s="2">
         <v>0</v>
       </c>
       <c r="AY43" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -7119,7 +7251,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -7128,52 +7260,52 @@
         <v>0</v>
       </c>
       <c r="E44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I44" s="2">
         <v>0</v>
       </c>
       <c r="J44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="2">
         <v>-1</v>
@@ -7182,10 +7314,10 @@
         <v>0</v>
       </c>
       <c r="W44" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="X44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="2">
         <v>-1</v>
@@ -7197,28 +7329,28 @@
         <v>-1</v>
       </c>
       <c r="AB44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" s="2">
         <v>-1</v>
       </c>
       <c r="AD44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG44" s="2">
         <v>0</v>
       </c>
       <c r="AH44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ44" s="2">
         <v>0</v>
@@ -7227,13 +7359,13 @@
         <v>0</v>
       </c>
       <c r="AL44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO44" s="2">
         <v>0</v>
@@ -7242,31 +7374,34 @@
         <v>0</v>
       </c>
       <c r="AQ44" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR44" s="2">
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT44" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AU44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV44" s="2">
         <v>0</v>
       </c>
       <c r="AW44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY44" s="2">
         <v>0</v>
+      </c>
+      <c r="AZ44" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -7277,58 +7412,58 @@
         <v>0</v>
       </c>
       <c r="C45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2">
         <v>-1</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
       </c>
       <c r="K45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N45" s="2">
         <v>-1</v>
       </c>
       <c r="O45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="2">
         <v>1</v>
       </c>
       <c r="Q45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R45" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S45" s="2">
         <v>1</v>
       </c>
       <c r="T45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="2">
         <v>-1</v>
@@ -7337,46 +7472,46 @@
         <v>0</v>
       </c>
       <c r="W45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
       </c>
       <c r="Y45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="2">
         <v>-1</v>
       </c>
       <c r="AB45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG45" s="2">
         <v>0</v>
       </c>
       <c r="AH45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="2">
         <v>0</v>
@@ -7385,42 +7520,45 @@
         <v>0</v>
       </c>
       <c r="AM45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" s="2">
         <v>0</v>
       </c>
       <c r="AP45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR45" s="2">
         <v>0</v>
       </c>
       <c r="AS45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT45" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV45" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AW45" s="2">
         <v>0</v>
       </c>
       <c r="AX45" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7432,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -7441,34 +7579,34 @@
         <v>-1</v>
       </c>
       <c r="F46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
       </c>
       <c r="K46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P46" s="2">
         <v>1</v>
@@ -7477,22 +7615,22 @@
         <v>0</v>
       </c>
       <c r="R46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="2">
         <v>0</v>
       </c>
       <c r="U46" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="V46" s="2">
         <v>0</v>
       </c>
       <c r="W46" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X46" s="2">
         <v>0</v>
@@ -7504,10 +7642,10 @@
         <v>1</v>
       </c>
       <c r="AA46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" s="2">
         <v>0</v>
@@ -7519,49 +7657,49 @@
         <v>0</v>
       </c>
       <c r="AF46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ46" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AR46" s="2">
         <v>-1</v>
       </c>
       <c r="AS46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU46" s="2">
         <v>1</v>
@@ -7570,13 +7708,16 @@
         <v>0</v>
       </c>
       <c r="AW46" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AX46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY46" s="2">
         <v>-1</v>
+      </c>
+      <c r="AZ46" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -7584,76 +7725,76 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="2">
         <v>0</v>
       </c>
       <c r="L47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N47" s="2">
         <v>0</v>
       </c>
       <c r="O47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U47" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="2">
         <v>1</v>
@@ -7668,70 +7809,73 @@
         <v>0</v>
       </c>
       <c r="AD47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF47" s="2">
         <v>1</v>
       </c>
       <c r="AG47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AJ47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AK47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM47" s="2">
         <v>1</v>
       </c>
       <c r="AN47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR47" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AS47" s="2">
         <v>-1</v>
       </c>
       <c r="AT47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" s="2">
         <v>0</v>
       </c>
       <c r="AX47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY47" s="2">
-        <v>-2</v>
+        <v>1</v>
+      </c>
+      <c r="AZ47" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -7745,31 +7889,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="2">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K48" s="2">
         <v>-1</v>
       </c>
       <c r="L48" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M48" s="2">
         <v>-1</v>
@@ -7778,13 +7922,13 @@
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="2">
         <v>0</v>
@@ -7793,25 +7937,25 @@
         <v>0</v>
       </c>
       <c r="T48" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U48" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AA48" s="2">
         <v>0</v>
@@ -7820,28 +7964,28 @@
         <v>1</v>
       </c>
       <c r="AC48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE48" s="2">
         <v>-1</v>
       </c>
       <c r="AF48" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AG48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AI48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK48" s="2">
         <v>0</v>
@@ -7850,19 +7994,19 @@
         <v>1</v>
       </c>
       <c r="AM48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO48" s="2">
         <v>1</v>
       </c>
       <c r="AP48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ48" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR48" s="2">
         <v>0</v>
@@ -7871,22 +8015,25 @@
         <v>0</v>
       </c>
       <c r="AT48" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AU48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV48" s="2">
         <v>0</v>
       </c>
       <c r="AW48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" s="2">
         <v>1</v>
       </c>
       <c r="AY48" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -7894,130 +8041,130 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2">
         <v>-1</v>
       </c>
       <c r="K49" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N49" s="2">
         <v>0</v>
       </c>
       <c r="O49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="U49" s="2">
         <v>-2</v>
       </c>
       <c r="V49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="2">
         <v>-1</v>
       </c>
       <c r="X49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="2">
         <v>0</v>
       </c>
       <c r="AB49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AC49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE49" s="2">
         <v>-1</v>
       </c>
       <c r="AF49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AH49" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AI49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AJ49" s="2">
         <v>-1</v>
       </c>
       <c r="AK49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AN49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AQ49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR49" s="2">
         <v>0</v>
@@ -8026,22 +8173,25 @@
         <v>0</v>
       </c>
       <c r="AT49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AU49" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW49" s="2">
         <v>0</v>
       </c>
       <c r="AX49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY49" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ49" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -8049,112 +8199,112 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D50" s="2">
         <v>-1</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2">
         <v>-1</v>
       </c>
       <c r="K50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2">
         <v>0</v>
       </c>
       <c r="M50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P50" s="2">
         <v>0</v>
       </c>
       <c r="Q50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="T50" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="U50" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="V50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X50" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Y50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Z50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AA50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AC50" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AD50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH50" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AI50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AJ50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL50" s="2">
         <v>-1</v>
@@ -8163,40 +8313,43 @@
         <v>-1</v>
       </c>
       <c r="AN50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO50" s="2">
         <v>0</v>
       </c>
       <c r="AP50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS50" s="2">
         <v>0</v>
       </c>
       <c r="AT50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU50" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AV50" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW50" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY50" s="2">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -8213,43 +8366,43 @@
         <v>-1</v>
       </c>
       <c r="E51" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G51" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K51" s="2">
         <v>1</v>
       </c>
       <c r="L51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R51" s="2">
         <v>0</v>
@@ -8264,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W51" s="2">
         <v>1</v>
@@ -8273,58 +8426,58 @@
         <v>2</v>
       </c>
       <c r="Y51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="2">
         <v>0</v>
       </c>
       <c r="AA51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB51" s="2">
         <v>0</v>
       </c>
       <c r="AC51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE51" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG51" s="2">
         <v>0</v>
       </c>
       <c r="AH51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AK51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO51" s="2">
         <v>0</v>
       </c>
       <c r="AP51" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ51" s="2">
         <v>-1</v>
@@ -8333,28 +8486,188 @@
         <v>0</v>
       </c>
       <c r="AS51" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT51" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV51" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AW51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AX51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY51" s="2">
         <v>-1</v>
       </c>
+      <c r="AZ51" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2">
+        <v>2</v>
+      </c>
+      <c r="H52" s="2">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2">
+        <v>1</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="O52" s="2">
+        <v>2</v>
+      </c>
+      <c r="P52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="T52" s="2">
+        <v>2</v>
+      </c>
+      <c r="U52" s="2">
+        <v>1</v>
+      </c>
+      <c r="V52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="W52" s="2">
+        <v>1</v>
+      </c>
+      <c r="X52" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AK52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AM52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AR52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AS52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AU52" s="2">
+        <v>2</v>
+      </c>
+      <c r="AV52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AX52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AZ52" s="2">
+        <v>-1</v>
+      </c>
+    </row>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -9303,6 +9616,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.5118055" right="0.5118055" top="0.7875" bottom="0.7875" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
@@ -2672,94 +2672,94 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D15" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M15" s="2">
         <v>0</v>
       </c>
       <c r="N15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
       </c>
       <c r="P15" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="2">
         <v>0</v>
       </c>
       <c r="S15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T15" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U15" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Z15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE15" s="2">
         <v>0</v>
       </c>
       <c r="AF15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG15" s="2">
         <v>0</v>
@@ -2768,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="AI15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="2">
         <v>0</v>
@@ -2789,37 +2789,37 @@
         <v>-1</v>
       </c>
       <c r="AP15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ15" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR15" s="2">
         <v>0</v>
       </c>
       <c r="AS15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AT15" s="2">
         <v>0</v>
       </c>
       <c r="AU15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV15" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY15" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AZ15" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -6524,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X39" s="2">
         <v>0</v>
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA39" s="2">
         <v>1</v>
@@ -6619,37 +6619,37 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
         <v>-2</v>
       </c>
       <c r="J40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2">
         <v>0</v>
@@ -6661,25 +6661,25 @@
         <v>-1</v>
       </c>
       <c r="P40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" s="2">
         <v>-1</v>
       </c>
       <c r="S40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="2">
         <v>-1</v>
@@ -6691,37 +6691,37 @@
         <v>-1</v>
       </c>
       <c r="Z40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AB40" s="2">
         <v>0</v>
       </c>
       <c r="AC40" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AD40" s="2">
         <v>1</v>
       </c>
       <c r="AE40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH40" s="2">
         <v>1</v>
       </c>
       <c r="AI40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK40" s="2">
         <v>0</v>
@@ -6730,25 +6730,25 @@
         <v>-1</v>
       </c>
       <c r="AM40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN40" s="2">
         <v>0</v>
       </c>
       <c r="AO40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR40" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AT40" s="2">
         <v>-1</v>
@@ -6757,19 +6757,19 @@
         <v>-1</v>
       </c>
       <c r="AV40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW40" s="2">
         <v>-1</v>
       </c>
       <c r="AX40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY40" s="2">
         <v>1</v>
       </c>
       <c r="AZ40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -7257,13 +7257,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
       </c>
       <c r="F44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2">
         <v>-2</v>
@@ -7275,10 +7275,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
@@ -7287,13 +7287,13 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="2">
         <v>0</v>
@@ -7308,10 +7308,10 @@
         <v>0</v>
       </c>
       <c r="U44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="2">
         <v>-2</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC44" s="2">
         <v>-1</v>
@@ -7365,22 +7365,22 @@
         <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ44" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AR44" s="2">
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT44" s="2">
         <v>-1</v>
@@ -7398,7 +7398,7 @@
         <v>-1</v>
       </c>
       <c r="AY44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ44" s="2">
         <v>2</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P4" s="2">
         <v>-1</v>
@@ -1668,7 +1668,7 @@
         <v>-1</v>
       </c>
       <c r="AK8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" s="3">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
@@ -5218,88 +5218,88 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S31" s="2">
         <v>0</v>
       </c>
       <c r="T31" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="U31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="2">
         <v>0</v>
       </c>
       <c r="X31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF31" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AG31" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AH31" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="2">
         <v>1</v>
       </c>
       <c r="AJ31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" s="2">
         <v>0</v>
@@ -5314,10 +5314,10 @@
         <v>0</v>
       </c>
       <c r="AO31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" s="2">
         <v>1</v>
@@ -5326,13 +5326,13 @@
         <v>-1</v>
       </c>
       <c r="AS31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT31" s="2">
         <v>0</v>
       </c>
       <c r="AU31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV31" s="2">
         <v>1</v>
@@ -5341,10 +5341,10 @@
         <v>1</v>
       </c>
       <c r="AX31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY31" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AZ31" s="2">
         <v>-1</v>
@@ -6461,7 +6461,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="2">
         <v>-1</v>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -6482,10 +6482,10 @@
         <v>1</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="2">
         <v>-2</v>
@@ -6494,10 +6494,10 @@
         <v>-2</v>
       </c>
       <c r="M39" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O39" s="2">
         <v>-1</v>
@@ -6518,25 +6518,25 @@
         <v>0</v>
       </c>
       <c r="U39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2">
         <v>0</v>
       </c>
       <c r="W39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" s="2">
         <v>0</v>
       </c>
       <c r="Y39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z39" s="2">
         <v>2</v>
       </c>
       <c r="AA39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="2">
         <v>0</v>
@@ -6545,16 +6545,16 @@
         <v>0</v>
       </c>
       <c r="AD39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE39" s="2">
         <v>2</v>
       </c>
       <c r="AF39" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AG39" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="2">
         <v>1</v>
@@ -6566,25 +6566,25 @@
         <v>2</v>
       </c>
       <c r="AK39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" s="2">
         <v>0</v>
       </c>
       <c r="AM39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" s="2">
         <v>1</v>
       </c>
       <c r="AO39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR39" s="2">
         <v>0</v>
@@ -6593,25 +6593,25 @@
         <v>-1</v>
       </c>
       <c r="AT39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU39" s="2">
         <v>-1</v>
       </c>
       <c r="AV39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ39" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -1563,7 +1563,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>2</v>
       </c>
       <c r="AW8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" s="2">
         <v>-1</v>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="AW27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX27" s="2">
         <v>-1</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162114F3-E830-4CE8-B8BE-A81287B6CFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ADC542-D341-48F2-8EDC-0D3CBF352B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6007,13 +6007,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
         <v>-1</v>
@@ -6022,7 +6022,7 @@
         <v>-1</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -6031,10 +6031,10 @@
         <v>-1</v>
       </c>
       <c r="J36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K36" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
@@ -6043,70 +6043,70 @@
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P36" s="2">
         <v>-1</v>
       </c>
       <c r="Q36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T36" s="2">
         <v>2</v>
       </c>
       <c r="U36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Y36" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Z36" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AA36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB36" s="2">
         <v>-1</v>
       </c>
       <c r="AC36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD36" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE36" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AF36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="2">
         <v>0</v>
@@ -6118,10 +6118,10 @@
         <v>-1</v>
       </c>
       <c r="AM36" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AN36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" s="2">
         <v>-1</v>
@@ -6130,34 +6130,34 @@
         <v>-1</v>
       </c>
       <c r="AQ36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT36" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AU36" s="2">
         <v>0</v>
       </c>
       <c r="AV36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY36" s="2">
         <v>-1</v>
       </c>
       <c r="AZ36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7057,7 +7057,7 @@
         <v>2</v>
       </c>
       <c r="AJ42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="2">
         <v>0</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ADC542-D341-48F2-8EDC-0D3CBF352B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C2A7A2-1F87-44AF-9090-91462F6B8B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,6 +94,9 @@
     <t>Lifeweaver</t>
   </si>
   <si>
+    <t>Lúcio</t>
+  </si>
+  <si>
     <t>Mauga</t>
   </si>
   <si>
@@ -174,9 +177,6 @@
   <si>
     <t>Zenyatta</t>
   </si>
-  <si>
-    <t>Lúcio</t>
-  </si>
 </sst>
 </file>
 
@@ -249,8 +249,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -546,88 +555,88 @@
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -641,7 +650,7 @@
         <v>-1</v>
       </c>
       <c r="D2" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E2" s="2">
         <v>2</v>
@@ -653,7 +662,7 @@
         <v>-1</v>
       </c>
       <c r="H2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -674,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="O2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P2" s="2">
         <v>-1</v>
@@ -710,7 +719,7 @@
         <v>-1</v>
       </c>
       <c r="AA2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB2" s="2">
         <v>1</v>
@@ -737,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="2">
         <v>0</v>
@@ -799,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -811,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -832,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2">
         <v>0</v>
@@ -868,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="AA3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC3" s="2">
         <v>1</v>
@@ -901,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" s="2">
         <v>1</v>
@@ -951,19 +960,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -981,7 +990,7 @@
         <v>-1</v>
       </c>
       <c r="L4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -993,16 +1002,16 @@
         <v>-1</v>
       </c>
       <c r="P4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
         <v>0</v>
       </c>
       <c r="S4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" s="2">
         <v>1</v>
@@ -1014,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="2">
         <v>1</v>
@@ -1026,16 +1035,16 @@
         <v>2</v>
       </c>
       <c r="AA4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="2">
         <v>1</v>
       </c>
       <c r="AD4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="2">
         <v>2</v>
@@ -1050,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="2">
         <v>0</v>
@@ -1065,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="AN4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP4" s="2">
         <v>0</v>
@@ -1095,10 +1104,10 @@
         <v>-1</v>
       </c>
       <c r="AX4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" s="2">
         <v>0</v>
@@ -1115,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="D5" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -1148,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P5" s="2">
         <v>-1</v>
@@ -1184,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="AA5" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2">
         <v>-1</v>
@@ -1342,7 +1351,7 @@
         <v>-1</v>
       </c>
       <c r="AA6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="2">
         <v>1</v>
@@ -1369,13 +1378,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK6" s="2">
         <v>0</v>
       </c>
       <c r="AL6" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AM6" s="2">
         <v>0</v>
@@ -1586,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>-1</v>
@@ -1747,7 +1756,7 @@
         <v>-2</v>
       </c>
       <c r="D9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -1780,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2">
         <v>0</v>
@@ -1816,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB9" s="2">
         <v>0</v>
@@ -1843,13 +1852,13 @@
         <v>-1</v>
       </c>
       <c r="AJ9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" s="2">
         <v>0</v>
       </c>
       <c r="AL9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="2">
         <v>0</v>
@@ -1905,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1938,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P10" s="2">
         <v>1</v>
@@ -1974,7 +1983,7 @@
         <v>2</v>
       </c>
       <c r="AA10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB10" s="2">
         <v>1</v>
@@ -2001,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK10" s="2">
         <v>0</v>
       </c>
       <c r="AL10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM10" s="2">
         <v>1</v>
@@ -2063,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -2132,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="2">
         <v>0</v>
@@ -2159,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AK11" s="2">
         <v>0</v>
       </c>
       <c r="AL11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" s="2">
         <v>0</v>
@@ -2215,70 +2224,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E12" s="2">
         <v>-1</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N12" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O12" s="2">
         <v>1</v>
       </c>
       <c r="P12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
       </c>
       <c r="R12" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
       </c>
       <c r="U12" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2">
         <v>1</v>
       </c>
       <c r="W12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X12" s="2">
         <v>1</v>
@@ -2302,64 +2311,64 @@
         <v>0</v>
       </c>
       <c r="AE12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AF12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN12" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AR12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS12" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT12" s="2">
         <v>0</v>
       </c>
       <c r="AU12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV12" s="2">
         <v>1</v>
       </c>
       <c r="AW12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX12" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY12" s="2">
         <v>0</v>
@@ -2475,7 +2484,7 @@
         <v>-1</v>
       </c>
       <c r="AJ13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="2">
         <v>0</v>
@@ -2537,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="2">
         <v>-1</v>
@@ -2570,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2">
         <v>1</v>
@@ -2606,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="AA14" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="2">
         <v>0</v>
@@ -2633,13 +2642,13 @@
         <v>-1</v>
       </c>
       <c r="AJ14" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="2">
         <v>0</v>
       </c>
       <c r="AL14" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM14" s="2">
         <v>1</v>
@@ -2701,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -2824,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" s="2">
         <v>-2</v>
@@ -2955,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="AL16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM16" s="2">
         <v>-1</v>
@@ -3011,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -3044,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="2">
         <v>0</v>
@@ -3080,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="2">
         <v>0</v>
@@ -3107,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK17" s="2">
         <v>0</v>
@@ -3271,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" s="2">
         <v>0</v>
@@ -3360,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2">
         <v>-1</v>
@@ -3396,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AB19" s="2">
         <v>-1</v>
@@ -3423,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="AJ19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK19" s="2">
         <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AM19" s="2">
         <v>1</v>
@@ -3485,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -3518,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2">
         <v>-1</v>
@@ -3581,13 +3590,13 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK20" s="2">
         <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM20" s="2">
         <v>-1</v>
@@ -3676,7 +3685,7 @@
         <v>-1</v>
       </c>
       <c r="O21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P21" s="2">
         <v>-1</v>
@@ -3739,7 +3748,7 @@
         <v>-1</v>
       </c>
       <c r="AJ21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" s="2">
         <v>0</v>
@@ -3834,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="2">
         <v>-2</v>
@@ -3870,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="2">
         <v>0</v>
@@ -3903,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AL22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" s="2">
         <v>1</v>
@@ -3959,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -3992,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="2">
         <v>0</v>
@@ -4028,7 +4037,7 @@
         <v>-2</v>
       </c>
       <c r="AA23" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AB23" s="2">
         <v>-1</v>
@@ -4055,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" s="2">
         <v>0</v>
       </c>
       <c r="AL23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" s="2">
         <v>-1</v>
@@ -4117,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E24" s="2">
         <v>-1</v>
@@ -4186,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AB24" s="2">
         <v>0</v>
@@ -4213,13 +4222,13 @@
         <v>1</v>
       </c>
       <c r="AJ24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24" s="2">
         <v>0</v>
       </c>
       <c r="AL24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM24" s="2">
         <v>0</v>
@@ -4266,7 +4275,7 @@
     </row>
     <row r="25" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>0</v>
@@ -4275,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -4308,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2">
         <v>0</v>
@@ -4344,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="AA25" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="2">
         <v>0</v>
@@ -4377,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="AL25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" s="2">
         <v>0</v>
@@ -4424,7 +4433,7 @@
     </row>
     <row r="26" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
@@ -4433,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -4502,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="AA26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB26" s="2">
         <v>1</v>
@@ -4529,13 +4538,13 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK26" s="2">
         <v>0</v>
       </c>
       <c r="AL26" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AM26" s="2">
         <v>0</v>
@@ -4582,10 +4591,10 @@
     </row>
     <row r="27" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -4594,7 +4603,7 @@
         <v>-1</v>
       </c>
       <c r="E27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2">
         <v>-1</v>
@@ -4603,7 +4612,7 @@
         <v>-1</v>
       </c>
       <c r="H27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -4612,10 +4621,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
@@ -4624,7 +4633,7 @@
         <v>-2</v>
       </c>
       <c r="O27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="2">
         <v>-1</v>
@@ -4639,7 +4648,7 @@
         <v>-2</v>
       </c>
       <c r="T27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" s="2">
         <v>-2</v>
@@ -4648,16 +4657,16 @@
         <v>-1</v>
       </c>
       <c r="W27" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X27" s="2">
         <v>-2</v>
       </c>
       <c r="Y27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA27" s="2">
         <v>0</v>
@@ -4672,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="AE27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF27" s="2">
         <v>-2</v>
@@ -4681,10 +4690,10 @@
         <v>2</v>
       </c>
       <c r="AH27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" s="2">
         <v>1</v>
@@ -4693,13 +4702,13 @@
         <v>0</v>
       </c>
       <c r="AL27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM27" s="2">
         <v>0</v>
       </c>
       <c r="AN27" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO27" s="2">
         <v>1</v>
@@ -4711,13 +4720,13 @@
         <v>0</v>
       </c>
       <c r="AR27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT27" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AU27" s="2">
         <v>0</v>
@@ -4740,7 +4749,7 @@
     </row>
     <row r="28" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>0</v>
@@ -4749,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -4782,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="2">
         <v>0</v>
@@ -4898,7 +4907,7 @@
     </row>
     <row r="29" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>-1</v>
@@ -4940,7 +4949,7 @@
         <v>2</v>
       </c>
       <c r="O29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="2">
         <v>-1</v>
@@ -5056,7 +5065,7 @@
     </row>
     <row r="30" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
@@ -5098,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="O30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="2">
         <v>1</v>
@@ -5134,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="AA30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="2">
         <v>0</v>
@@ -5161,13 +5170,13 @@
         <v>1</v>
       </c>
       <c r="AJ30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK30" s="2">
         <v>0</v>
       </c>
       <c r="AL30" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM30" s="2">
         <v>1</v>
@@ -5214,7 +5223,7 @@
     </row>
     <row r="31" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
@@ -5223,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -5319,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK31" s="2">
         <v>0</v>
@@ -5372,7 +5381,7 @@
     </row>
     <row r="32" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>0</v>
@@ -5414,7 +5423,7 @@
         <v>-1</v>
       </c>
       <c r="O32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" s="2">
         <v>1</v>
@@ -5450,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="AA32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB32" s="2">
         <v>0</v>
@@ -5477,13 +5486,13 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" s="2">
         <v>0</v>
       </c>
       <c r="AL32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" s="2">
         <v>1</v>
@@ -5530,7 +5539,7 @@
     </row>
     <row r="33" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>0</v>
@@ -5641,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AM33" s="2">
         <v>1</v>
@@ -5688,7 +5697,7 @@
     </row>
     <row r="34" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>-1</v>
@@ -5697,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
@@ -5730,7 +5739,7 @@
         <v>2</v>
       </c>
       <c r="O34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="2">
         <v>-1</v>
@@ -5793,13 +5802,13 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK34" s="2">
         <v>0</v>
       </c>
       <c r="AL34" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM34" s="2">
         <v>0</v>
@@ -5846,7 +5855,7 @@
     </row>
     <row r="35" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>0</v>
@@ -5888,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="2">
         <v>-1</v>
@@ -5924,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="AA35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="2">
         <v>0</v>
@@ -5957,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="AL35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" s="2">
         <v>-2</v>
@@ -6004,7 +6013,7 @@
     </row>
     <row r="36" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>-2</v>
@@ -6025,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="2">
         <v>-1</v>
@@ -6037,7 +6046,7 @@
         <v>2</v>
       </c>
       <c r="L36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -6055,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="R36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="2">
         <v>-1</v>
@@ -6067,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W36" s="2">
         <v>-1</v>
@@ -6088,7 +6097,7 @@
         <v>-1</v>
       </c>
       <c r="AC36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD36" s="2">
         <v>1</v>
@@ -6106,7 +6115,7 @@
         <v>-1</v>
       </c>
       <c r="AI36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ36" s="2">
         <v>0</v>
@@ -6118,7 +6127,7 @@
         <v>-1</v>
       </c>
       <c r="AM36" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AN36" s="2">
         <v>0</v>
@@ -6127,7 +6136,7 @@
         <v>-1</v>
       </c>
       <c r="AP36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ36" s="2">
         <v>1</v>
@@ -6151,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="AX36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY36" s="2">
         <v>-1</v>
@@ -6162,7 +6171,7 @@
     </row>
     <row r="37" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
@@ -6320,7 +6329,7 @@
     </row>
     <row r="38" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
@@ -6365,13 +6374,13 @@
         <v>0</v>
       </c>
       <c r="P38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="2">
         <v>1</v>
       </c>
       <c r="R38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="2">
         <v>-2</v>
@@ -6398,7 +6407,7 @@
         <v>2</v>
       </c>
       <c r="AA38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB38" s="2">
         <v>0</v>
@@ -6407,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AD38" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" s="2">
         <v>-1</v>
@@ -6452,22 +6461,22 @@
         <v>0</v>
       </c>
       <c r="AS38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT38" s="2">
         <v>0</v>
       </c>
       <c r="AU38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV38" s="2">
         <v>0</v>
       </c>
       <c r="AW38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY38" s="2">
         <v>-2</v>
@@ -6478,7 +6487,7 @@
     </row>
     <row r="39" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -6636,7 +6645,7 @@
     </row>
     <row r="40" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -6741,7 +6750,7 @@
         <v>1</v>
       </c>
       <c r="AJ40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" s="2">
         <v>0</v>
@@ -6794,106 +6803,106 @@
     </row>
     <row r="41" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
         <v>-2</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="I41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R41" s="2">
         <v>-1</v>
       </c>
       <c r="S41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U41" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="V41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W41" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="X41" s="2">
         <v>2</v>
       </c>
       <c r="Y41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AA41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AB41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD41" s="2">
         <v>1</v>
       </c>
       <c r="AE41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF41" s="2">
         <v>1</v>
       </c>
       <c r="AG41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI41" s="2">
         <v>0</v>
@@ -6902,49 +6911,49 @@
         <v>1</v>
       </c>
       <c r="AK41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AM41" s="2">
         <v>-2</v>
       </c>
       <c r="AN41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO41" s="2">
         <v>0</v>
       </c>
       <c r="AP41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AR41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS41" s="2">
         <v>1</v>
       </c>
       <c r="AT41" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AU41" s="2">
         <v>2</v>
       </c>
       <c r="AV41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ41" s="2">
         <v>2</v>
@@ -6952,7 +6961,7 @@
     </row>
     <row r="42" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
@@ -6994,7 +7003,7 @@
         <v>-1</v>
       </c>
       <c r="O42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="2">
         <v>0</v>
@@ -7110,7 +7119,7 @@
     </row>
     <row r="43" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
@@ -7152,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" s="2">
         <v>-1</v>
@@ -7188,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="AA43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="2">
         <v>1</v>
@@ -7215,13 +7224,13 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK43" s="2">
         <v>0</v>
       </c>
       <c r="AL43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM43" s="2">
         <v>0</v>
@@ -7268,7 +7277,7 @@
     </row>
     <row r="44" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
@@ -7286,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="2">
         <v>-2</v>
@@ -7307,13 +7316,13 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="2">
         <v>0</v>
@@ -7346,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" s="2">
         <v>-1</v>
@@ -7373,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" s="2">
         <v>0</v>
@@ -7385,13 +7394,13 @@
         <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO44" s="2">
         <v>-1</v>
       </c>
       <c r="AP44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ44" s="2">
         <v>-1</v>
@@ -7400,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT44" s="2">
         <v>-1</v>
@@ -7418,7 +7427,7 @@
         <v>-1</v>
       </c>
       <c r="AY44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ44" s="2">
         <v>2</v>
@@ -7426,43 +7435,43 @@
     </row>
     <row r="45" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2">
         <v>-2</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="2">
         <v>-1</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" s="2">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M45" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2">
         <v>-1</v>
@@ -7477,34 +7486,34 @@
         <v>-1</v>
       </c>
       <c r="R45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V45" s="2">
         <v>0</v>
       </c>
       <c r="W45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
       </c>
       <c r="Y45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="2">
         <v>0</v>
       </c>
       <c r="AA45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="2">
         <v>0</v>
@@ -7513,46 +7522,46 @@
         <v>-1</v>
       </c>
       <c r="AD45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE45" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AF45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG45" s="2">
         <v>0</v>
       </c>
       <c r="AH45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI45" s="2">
         <v>-1</v>
       </c>
       <c r="AJ45" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AK45" s="2">
         <v>0</v>
       </c>
       <c r="AL45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM45" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP45" s="2">
         <v>0</v>
       </c>
       <c r="AQ45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR45" s="2">
         <v>0</v>
@@ -7564,30 +7573,30 @@
         <v>-1</v>
       </c>
       <c r="AU45" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW45" s="2">
         <v>0</v>
       </c>
       <c r="AX45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C46" s="2">
         <v>-1</v>
@@ -7662,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="AA46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="2">
         <v>1</v>
@@ -7689,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AK46" s="2">
         <v>0</v>
@@ -7742,7 +7751,7 @@
     </row>
     <row r="47" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>0</v>
@@ -7751,7 +7760,7 @@
         <v>2</v>
       </c>
       <c r="D47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2">
         <v>-1</v>
@@ -7900,7 +7909,7 @@
     </row>
     <row r="48" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>
@@ -8011,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="AL48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" s="2">
         <v>0</v>
@@ -8058,7 +8067,7 @@
     </row>
     <row r="49" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
@@ -8067,127 +8076,127 @@
         <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M49" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="2">
         <v>2</v>
       </c>
       <c r="Q49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T49" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="U49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AA49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" s="2">
         <v>1</v>
       </c>
       <c r="AC49" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AF49" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AG49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AH49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ49" s="2">
         <v>-1</v>
       </c>
       <c r="AK49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM49" s="2">
         <v>1</v>
       </c>
       <c r="AN49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP49" s="2">
         <v>1</v>
       </c>
       <c r="AQ49" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AR49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS49" s="2">
         <v>0</v>
@@ -8199,7 +8208,7 @@
         <v>2</v>
       </c>
       <c r="AV49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW49" s="2">
         <v>0</v>
@@ -8208,15 +8217,15 @@
         <v>1</v>
       </c>
       <c r="AY49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AZ49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
         <v>-1</v>
@@ -8294,7 +8303,7 @@
         <v>-2</v>
       </c>
       <c r="AA50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" s="2">
         <v>-2</v>
@@ -8321,13 +8330,13 @@
         <v>-2</v>
       </c>
       <c r="AJ50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AK50" s="2">
         <v>0</v>
       </c>
       <c r="AL50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM50" s="2">
         <v>-1</v>
@@ -8374,7 +8383,7 @@
     </row>
     <row r="51" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
@@ -8416,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="2">
         <v>0</v>
@@ -8452,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="AA51" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AB51" s="2">
         <v>0</v>
@@ -8479,13 +8488,13 @@
         <v>0</v>
       </c>
       <c r="AJ51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK51" s="2">
         <v>0</v>
       </c>
       <c r="AL51" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AM51" s="2">
         <v>-1</v>
@@ -8532,7 +8541,7 @@
     </row>
     <row r="52" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
         <v>1</v>
@@ -8541,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="2">
         <v>-2</v>
@@ -8574,7 +8583,7 @@
         <v>-1</v>
       </c>
       <c r="O52" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P52" s="2">
         <v>-1</v>
@@ -8637,13 +8646,13 @@
         <v>1</v>
       </c>
       <c r="AJ52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AK52" s="2">
         <v>0</v>
       </c>
       <c r="AL52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM52" s="2">
         <v>0</v>
@@ -9638,7 +9647,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <conditionalFormatting sqref="B2:AZ52">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.51180550000000002" right="0.51180550000000002" top="0.78749999999999998" bottom="0.78749999999999998" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C2A7A2-1F87-44AF-9090-91462F6B8B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B70E4A2-550C-4D60-9E0C-13E1A03761F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1 (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -674,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
@@ -752,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="AL2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="2">
         <v>0</v>
@@ -761,16 +774,16 @@
         <v>0</v>
       </c>
       <c r="AO2" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="2">
         <v>0</v>
       </c>
       <c r="AR2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS2" s="2">
         <v>1</v>
@@ -922,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="AP3" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AQ3" s="2">
         <v>0</v>
@@ -1148,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
@@ -1235,10 +1248,10 @@
         <v>-1</v>
       </c>
       <c r="AO5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" s="2">
         <v>-1</v>
@@ -1294,7 +1307,7 @@
         <v>-1</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -1306,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2">
         <v>0</v>
@@ -1387,13 +1400,13 @@
         <v>-2</v>
       </c>
       <c r="AM6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN6" s="2">
         <v>-1</v>
       </c>
       <c r="AO6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" s="2">
         <v>1</v>
@@ -1402,7 +1415,7 @@
         <v>-1</v>
       </c>
       <c r="AR6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS6" s="2">
         <v>1</v>
@@ -1452,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -1464,7 +1477,7 @@
         <v>-1</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M7" s="2">
         <v>-1</v>
@@ -1551,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP7" s="2">
         <v>0</v>
@@ -1604,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -1613,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J8" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
@@ -1637,7 +1650,7 @@
         <v>-1</v>
       </c>
       <c r="Q8" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2">
         <v>0</v>
@@ -1649,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V8" s="2">
         <v>1</v>
@@ -1661,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2">
         <v>1</v>
@@ -1703,40 +1716,40 @@
         <v>0</v>
       </c>
       <c r="AM8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN8" s="2">
         <v>0</v>
       </c>
       <c r="AO8" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8" s="2">
         <v>0</v>
       </c>
       <c r="AR8" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AS8" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT8" s="2">
         <v>0</v>
       </c>
       <c r="AU8" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AV8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW8" s="2">
         <v>1</v>
       </c>
       <c r="AX8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY8" s="2">
         <v>-1</v>
@@ -1768,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1780,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
@@ -1867,16 +1880,16 @@
         <v>1</v>
       </c>
       <c r="AO9" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AQ9" s="2">
         <v>-1</v>
       </c>
       <c r="AR9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" s="2">
         <v>1</v>
@@ -1926,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2">
         <v>-1</v>
@@ -1938,7 +1951,7 @@
         <v>-1</v>
       </c>
       <c r="L10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2">
         <v>2</v>
@@ -2025,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP10" s="2">
         <v>0</v>
@@ -2034,7 +2047,7 @@
         <v>-2</v>
       </c>
       <c r="AR10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS10" s="2">
         <v>-1</v>
@@ -2084,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I11" s="2">
         <v>-1</v>
@@ -2096,7 +2109,7 @@
         <v>-1</v>
       </c>
       <c r="L11" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M11" s="2">
         <v>-1</v>
@@ -2177,22 +2190,22 @@
         <v>1</v>
       </c>
       <c r="AM11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN11" s="2">
         <v>0</v>
       </c>
       <c r="AO11" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AP11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ11" s="2">
         <v>-1</v>
       </c>
       <c r="AR11" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS11" s="2">
         <v>0</v>
@@ -2236,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G12" s="2">
         <v>2</v>
@@ -2266,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
@@ -2275,7 +2288,7 @@
         <v>-2</v>
       </c>
       <c r="S12" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
@@ -2287,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="W12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2">
         <v>1</v>
       </c>
       <c r="Y12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
@@ -2308,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="AD12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="2">
         <v>1</v>
@@ -2317,13 +2330,13 @@
         <v>1</v>
       </c>
       <c r="AG12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="2">
         <v>0</v>
       </c>
       <c r="AI12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ12" s="2">
         <v>1</v>
@@ -2356,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="AT12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" s="2">
         <v>-1</v>
@@ -2368,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="AX12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY12" s="2">
         <v>0</v>
@@ -2412,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2">
         <v>0</v>
@@ -2499,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="AO13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13" s="2">
         <v>0</v>
@@ -2508,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AR13" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="2">
         <v>-1</v>
@@ -2558,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I14" s="2">
         <v>-1</v>
@@ -2570,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2">
         <v>0</v>
@@ -2657,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="AO14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="2">
         <v>1</v>
@@ -2874,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
         <v>-2</v>
@@ -2886,7 +2899,7 @@
         <v>-2</v>
       </c>
       <c r="L16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M16" s="2">
         <v>0</v>
@@ -2973,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP16" s="2">
         <v>1</v>
@@ -2982,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="AR16" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS16" s="2">
         <v>-2</v>
@@ -3032,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I17" s="2">
         <v>-1</v>
@@ -3131,16 +3144,16 @@
         <v>-1</v>
       </c>
       <c r="AO17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" s="2">
         <v>-1</v>
       </c>
       <c r="AR17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS17" s="2">
         <v>1</v>
@@ -3190,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -3202,7 +3215,7 @@
         <v>-1</v>
       </c>
       <c r="L18" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2">
         <v>1</v>
@@ -3289,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="AO18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" s="2">
         <v>1</v>
@@ -3298,7 +3311,7 @@
         <v>-1</v>
       </c>
       <c r="AR18" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS18" s="2">
         <v>-2</v>
@@ -3348,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I19" s="2">
         <v>-1</v>
@@ -3360,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2">
         <v>0</v>
@@ -3450,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="AP19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ19" s="2">
         <v>1</v>
@@ -3605,10 +3618,10 @@
         <v>-2</v>
       </c>
       <c r="AO20" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ20" s="2">
         <v>0</v>
@@ -3664,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2">
         <v>-2</v>
@@ -3676,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M21" s="2">
         <v>1</v>
@@ -3763,7 +3776,7 @@
         <v>-1</v>
       </c>
       <c r="AO21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP21" s="2">
         <v>2</v>
@@ -3772,7 +3785,7 @@
         <v>-1</v>
       </c>
       <c r="AR21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS21" s="2">
         <v>2</v>
@@ -3822,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -3834,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M22" s="2">
         <v>-1</v>
@@ -3921,16 +3934,16 @@
         <v>0</v>
       </c>
       <c r="AO22" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AP22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" s="2">
         <v>1</v>
       </c>
       <c r="AR22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS22" s="2">
         <v>0</v>
@@ -3980,7 +3993,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
         <v>-1</v>
@@ -4079,16 +4092,16 @@
         <v>2</v>
       </c>
       <c r="AO23" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AP23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ23" s="2">
         <v>-1</v>
       </c>
       <c r="AR23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS23" s="2">
         <v>1</v>
@@ -4138,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
         <v>-1</v>
@@ -4150,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -4237,7 +4250,7 @@
         <v>-1</v>
       </c>
       <c r="AO24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP24" s="2">
         <v>1</v>
@@ -4395,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="AO25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" s="2">
         <v>0</v>
@@ -4454,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
@@ -4553,10 +4566,10 @@
         <v>1</v>
       </c>
       <c r="AO26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ26" s="2">
         <v>0</v>
@@ -4729,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV27" s="2">
         <v>0</v>
@@ -4872,13 +4885,13 @@
         <v>-1</v>
       </c>
       <c r="AP28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ28" s="2">
         <v>0</v>
       </c>
       <c r="AR28" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS28" s="2">
         <v>0</v>
@@ -4940,7 +4953,7 @@
         <v>-1</v>
       </c>
       <c r="L29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M29" s="2">
         <v>1</v>
@@ -5036,7 +5049,7 @@
         <v>-1</v>
       </c>
       <c r="AR29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS29" s="2">
         <v>1</v>
@@ -5086,7 +5099,7 @@
         <v>-1</v>
       </c>
       <c r="H30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>-1</v>
@@ -5098,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M30" s="2">
         <v>1</v>
@@ -5185,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="AO30" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AP30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ30" s="2">
         <v>0</v>
@@ -5244,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -5343,16 +5356,16 @@
         <v>0</v>
       </c>
       <c r="AO31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ31" s="2">
         <v>1</v>
       </c>
       <c r="AR31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS31" s="2">
         <v>1</v>
@@ -5402,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I32" s="2">
         <v>-1</v>
@@ -5414,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>
@@ -5510,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="AR32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="2">
         <v>1</v>
@@ -5662,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="AP33" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AQ33" s="2">
         <v>-1</v>
@@ -5718,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -5817,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP34" s="2">
         <v>-1</v>
@@ -5888,7 +5901,7 @@
         <v>-2</v>
       </c>
       <c r="L35" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="M35" s="2">
         <v>-1</v>
@@ -5978,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="AP35" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ35" s="2">
         <v>-2</v>
@@ -6192,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>
@@ -6204,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -6291,10 +6304,10 @@
         <v>0</v>
       </c>
       <c r="AO37" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37" s="2">
         <v>0</v>
@@ -6332,7 +6345,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="2">
         <v>-1</v>
@@ -6520,7 +6533,7 @@
         <v>-2</v>
       </c>
       <c r="L39" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2">
         <v>-1</v>
@@ -6595,7 +6608,7 @@
         <v>2</v>
       </c>
       <c r="AK39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL39" s="2">
         <v>0</v>
@@ -6607,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="AO39" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP39" s="2">
         <v>1</v>
@@ -6616,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="AR39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="2">
         <v>-1</v>
@@ -6678,7 +6691,7 @@
         <v>-2</v>
       </c>
       <c r="L40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2">
         <v>0</v>
@@ -6765,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="AO40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP40" s="2">
         <v>1</v>
@@ -6806,10 +6819,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -6818,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>-2</v>
@@ -6827,7 +6840,7 @@
         <v>-2</v>
       </c>
       <c r="I41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="2">
         <v>-1</v>
@@ -6839,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N41" s="2">
         <v>0</v>
@@ -6860,19 +6873,19 @@
         <v>0</v>
       </c>
       <c r="T41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2">
         <v>1</v>
       </c>
       <c r="W41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" s="2">
         <v>1</v>
@@ -6893,13 +6906,13 @@
         <v>1</v>
       </c>
       <c r="AE41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AF41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="2">
         <v>-1</v>
@@ -6932,7 +6945,7 @@
         <v>-1</v>
       </c>
       <c r="AR41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS41" s="2">
         <v>1</v>
@@ -6950,7 +6963,7 @@
         <v>2</v>
       </c>
       <c r="AX41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY41" s="2">
         <v>-1</v>
@@ -6976,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -6988,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="2">
         <v>-2</v>
@@ -7006,19 +7019,19 @@
         <v>1</v>
       </c>
       <c r="P42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q42" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S42" s="2">
         <v>-1</v>
       </c>
       <c r="T42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" s="2">
         <v>-2</v>
@@ -7030,10 +7043,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y42" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="2">
         <v>1</v>
@@ -7045,10 +7058,10 @@
         <v>-1</v>
       </c>
       <c r="AC42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42" s="2">
         <v>1</v>
@@ -7057,10 +7070,10 @@
         <v>-2</v>
       </c>
       <c r="AG42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="2">
         <v>2</v>
@@ -7069,19 +7082,19 @@
         <v>0</v>
       </c>
       <c r="AK42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL42" s="2">
         <v>2</v>
       </c>
       <c r="AM42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP42" s="2">
         <v>0</v>
@@ -7099,10 +7112,10 @@
         <v>-2</v>
       </c>
       <c r="AU42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW42" s="2">
         <v>-2</v>
@@ -7111,7 +7124,7 @@
         <v>-1</v>
       </c>
       <c r="AY42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ42" s="2">
         <v>-1</v>
@@ -7140,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -7152,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M43" s="2">
         <v>1</v>
@@ -7242,13 +7255,13 @@
         <v>1</v>
       </c>
       <c r="AP43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ43" s="2">
         <v>0</v>
       </c>
       <c r="AR43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="2">
         <v>1</v>
@@ -7304,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
@@ -7328,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="R44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S44" s="2">
         <v>-1</v>
@@ -7358,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="AB44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="2">
         <v>-1</v>
@@ -7394,13 +7407,13 @@
         <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ44" s="2">
         <v>-1</v>
@@ -7421,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="AW44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" s="2">
         <v>-1</v>
@@ -7468,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M45" s="2">
         <v>0</v>
@@ -7713,16 +7726,16 @@
         <v>0</v>
       </c>
       <c r="AO46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP46" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ46" s="2">
         <v>-1</v>
       </c>
       <c r="AR46" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS46" s="2">
         <v>0</v>
@@ -7772,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -7871,7 +7884,7 @@
         <v>1</v>
       </c>
       <c r="AO47" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP47" s="2">
         <v>1</v>
@@ -7880,7 +7893,7 @@
         <v>1</v>
       </c>
       <c r="AR47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS47" s="2">
         <v>-1</v>
@@ -7930,7 +7943,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2">
         <v>0</v>
@@ -8029,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="AO48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP48" s="2">
         <v>2</v>
@@ -8100,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2">
         <v>2</v>
@@ -8109,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="2">
         <v>2</v>
@@ -8175,10 +8188,10 @@
         <v>-1</v>
       </c>
       <c r="AK49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM49" s="2">
         <v>1</v>
@@ -8190,7 +8203,7 @@
         <v>-2</v>
       </c>
       <c r="AP49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ49" s="2">
         <v>-2</v>
@@ -8246,7 +8259,7 @@
         <v>-2</v>
       </c>
       <c r="H50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2">
         <v>0</v>
@@ -8258,7 +8271,7 @@
         <v>2</v>
       </c>
       <c r="L50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M50" s="2">
         <v>2</v>
@@ -8348,13 +8361,13 @@
         <v>0</v>
       </c>
       <c r="AP50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ50" s="2">
         <v>-2</v>
       </c>
       <c r="AR50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS50" s="2">
         <v>0</v>
@@ -8404,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="2">
         <v>1</v>
@@ -8503,10 +8516,10 @@
         <v>-1</v>
       </c>
       <c r="AO51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ51" s="2">
         <v>-1</v>
@@ -8574,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M52" s="2">
         <v>0</v>
@@ -8661,16 +8674,16 @@
         <v>1</v>
       </c>
       <c r="AO52" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AP52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ52" s="2">
         <v>-2</v>
       </c>
       <c r="AR52" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS52" s="2">
         <v>0</v>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -1,39 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projetos\Overwatch-Best-Picks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B70E4A2-550C-4D60-9E0C-13E1A03761F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Página1 (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Hero</t>
   </si>
@@ -194,8 +179,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -236,13 +221,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -273,14 +252,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -478,23 +449,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AZ1001"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.57031" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="7" width="12.5703125" customWidth="1"/>
+    <col min="1" max="7" width="12.57031" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +620,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -675,7 +643,7 @@
         <v>-1</v>
       </c>
       <c r="H2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -690,7 +658,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2">
         <v>2</v>
@@ -810,7 +778,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -968,7 +936,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1021,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S4" s="2">
         <v>1</v>
@@ -1036,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="2">
         <v>1</v>
@@ -1063,7 +1031,7 @@
         <v>2</v>
       </c>
       <c r="AF4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG4" s="2">
         <v>1</v>
@@ -1093,7 +1061,7 @@
         <v>-1</v>
       </c>
       <c r="AP4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" s="2">
         <v>0</v>
@@ -1126,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1164,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N5" s="2">
         <v>1</v>
@@ -1284,7 +1252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1322,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N6" s="2">
         <v>-1</v>
@@ -1442,7 +1410,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1567,7 +1535,7 @@
         <v>2</v>
       </c>
       <c r="AP7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" s="2">
         <v>-1</v>
@@ -1600,12 +1568,12 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1638,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N8" s="2">
         <v>1</v>
@@ -1710,7 +1678,7 @@
         <v>-1</v>
       </c>
       <c r="AK8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" s="3">
         <v>0</v>
@@ -1725,7 +1693,7 @@
         <v>2</v>
       </c>
       <c r="AP8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" s="2">
         <v>0</v>
@@ -1758,7 +1726,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1796,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2">
         <v>0</v>
@@ -1916,7 +1884,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1954,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
         <v>0</v>
@@ -2041,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="AP10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ10" s="2">
         <v>-2</v>
@@ -2074,7 +2042,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2112,7 +2080,7 @@
         <v>-1</v>
       </c>
       <c r="M11" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2">
         <v>1</v>
@@ -2205,7 +2173,7 @@
         <v>-1</v>
       </c>
       <c r="AR11" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS11" s="2">
         <v>0</v>
@@ -2232,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2357,7 +2325,7 @@
         <v>-1</v>
       </c>
       <c r="AP12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ12" s="2">
         <v>1</v>
@@ -2390,12 +2358,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -2404,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -2413,16 +2381,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2">
         <v>-1</v>
       </c>
       <c r="J13" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2">
         <v>2</v>
@@ -2446,22 +2414,22 @@
         <v>0</v>
       </c>
       <c r="S13" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" s="2">
         <v>1</v>
       </c>
       <c r="U13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="2">
         <v>0</v>
@@ -2476,25 +2444,25 @@
         <v>-1</v>
       </c>
       <c r="AC13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="2">
         <v>1</v>
       </c>
       <c r="AF13" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="2">
         <v>0</v>
       </c>
       <c r="AI13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="2">
         <v>0</v>
@@ -2506,22 +2474,22 @@
         <v>0</v>
       </c>
       <c r="AM13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN13" s="2">
         <v>0</v>
       </c>
       <c r="AO13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="2">
         <v>-1</v>
@@ -2530,7 +2498,7 @@
         <v>-1</v>
       </c>
       <c r="AU13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV13" s="2">
         <v>0</v>
@@ -2548,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2586,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N14" s="2">
         <v>0</v>
@@ -2706,7 +2674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2792,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD15" s="2">
         <v>-1</v>
@@ -2864,7 +2832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -3022,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -3060,7 +3028,7 @@
         <v>-1</v>
       </c>
       <c r="M17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2">
         <v>0</v>
@@ -3102,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="2">
         <v>0</v>
@@ -3180,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -3218,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2">
         <v>1</v>
@@ -3338,7 +3306,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -3376,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N19" s="2">
         <v>0</v>
@@ -3496,7 +3464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3534,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N20" s="2">
         <v>0</v>
@@ -3654,7 +3622,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -3692,7 +3660,7 @@
         <v>-2</v>
       </c>
       <c r="M21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N21" s="2">
         <v>-1</v>
@@ -3779,7 +3747,7 @@
         <v>-1</v>
       </c>
       <c r="AP21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ21" s="2">
         <v>-1</v>
@@ -3812,7 +3780,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -3850,7 +3818,7 @@
         <v>-1</v>
       </c>
       <c r="M22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
@@ -3937,7 +3905,7 @@
         <v>-1</v>
       </c>
       <c r="AP22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" s="2">
         <v>1</v>
@@ -3970,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -4008,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N23" s="2">
         <v>0</v>
@@ -4128,7 +4096,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -4166,7 +4134,7 @@
         <v>-1</v>
       </c>
       <c r="M24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N24" s="2">
         <v>-1</v>
@@ -4253,7 +4221,7 @@
         <v>-1</v>
       </c>
       <c r="AP24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ24" s="2">
         <v>-1</v>
@@ -4286,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -4324,7 +4292,7 @@
         <v>-1</v>
       </c>
       <c r="M25" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2">
         <v>1</v>
@@ -4444,7 +4412,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -4482,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N26" s="2">
         <v>0</v>
@@ -4602,7 +4570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -4652,7 +4620,7 @@
         <v>-1</v>
       </c>
       <c r="Q27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R27" s="2">
         <v>0</v>
@@ -4727,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="AP27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27" s="2">
         <v>0</v>
@@ -4745,7 +4713,7 @@
         <v>-1</v>
       </c>
       <c r="AV27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW27" s="2">
         <v>-1</v>
@@ -4760,7 +4728,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -4918,7 +4886,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -4956,13 +4924,13 @@
         <v>-1</v>
       </c>
       <c r="M29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N29" s="2">
         <v>2</v>
       </c>
       <c r="O29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="2">
         <v>-1</v>
@@ -5076,7 +5044,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -5114,7 +5082,7 @@
         <v>-1</v>
       </c>
       <c r="M30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N30" s="2">
         <v>2</v>
@@ -5234,7 +5202,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -5392,7 +5360,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -5430,7 +5398,7 @@
         <v>-1</v>
       </c>
       <c r="M32" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N32" s="2">
         <v>-1</v>
@@ -5550,7 +5518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -5588,7 +5556,7 @@
         <v>-1</v>
       </c>
       <c r="M33" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N33" s="2">
         <v>1</v>
@@ -5708,7 +5676,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -5866,7 +5834,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -5904,7 +5872,7 @@
         <v>-1</v>
       </c>
       <c r="M35" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="2">
         <v>0</v>
@@ -6024,7 +5992,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -6182,7 +6150,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -6205,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>
@@ -6340,7 +6308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -6498,7 +6466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -6536,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2">
         <v>-1</v>
@@ -6656,7 +6624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -6814,7 +6782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -6852,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2">
         <v>0</v>
@@ -6939,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="AP41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ41" s="2">
         <v>-1</v>
@@ -6972,7 +6940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -6983,7 +6951,7 @@
         <v>-1</v>
       </c>
       <c r="D42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -6992,25 +6960,25 @@
         <v>-1</v>
       </c>
       <c r="G42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I42" s="2">
         <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2">
         <v>-2</v>
       </c>
       <c r="L42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N42" s="2">
         <v>-1</v>
@@ -7034,16 +7002,16 @@
         <v>1</v>
       </c>
       <c r="U42" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W42" s="2">
         <v>0</v>
       </c>
       <c r="X42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="2">
         <v>0</v>
@@ -7052,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="AA42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB42" s="2">
         <v>-1</v>
@@ -7094,7 +7062,7 @@
         <v>-1</v>
       </c>
       <c r="AO42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP42" s="2">
         <v>0</v>
@@ -7103,7 +7071,7 @@
         <v>-1</v>
       </c>
       <c r="AR42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS42" s="2">
         <v>0</v>
@@ -7115,13 +7083,13 @@
         <v>-1</v>
       </c>
       <c r="AV42" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW42" s="2">
         <v>-2</v>
       </c>
       <c r="AX42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY42" s="2">
         <v>1</v>
@@ -7130,7 +7098,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="43" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -7168,7 +7136,7 @@
         <v>-1</v>
       </c>
       <c r="M43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N43" s="2">
         <v>0</v>
@@ -7288,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -7320,16 +7288,16 @@
         <v>0</v>
       </c>
       <c r="K44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
       </c>
       <c r="M44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
@@ -7371,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="AB44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC44" s="2">
         <v>-1</v>
@@ -7413,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="AP44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ44" s="2">
         <v>-1</v>
@@ -7446,7 +7414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -7484,7 +7452,7 @@
         <v>-2</v>
       </c>
       <c r="M45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2">
         <v>-1</v>
@@ -7604,7 +7572,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -7642,7 +7610,7 @@
         <v>-1</v>
       </c>
       <c r="M46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2">
         <v>-1</v>
@@ -7762,7 +7730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -7800,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2">
         <v>0</v>
@@ -7842,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AA47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" s="2">
         <v>0</v>
@@ -7920,7 +7888,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -7958,7 +7926,7 @@
         <v>-1</v>
       </c>
       <c r="M48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2">
         <v>0</v>
@@ -8000,7 +7968,7 @@
         <v>-2</v>
       </c>
       <c r="AA48" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB48" s="2">
         <v>1</v>
@@ -8045,7 +8013,7 @@
         <v>2</v>
       </c>
       <c r="AP48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ48" s="2">
         <v>-1</v>
@@ -8078,7 +8046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
@@ -8116,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N49" s="2">
         <v>1</v>
@@ -8236,7 +8204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -8274,7 +8242,7 @@
         <v>-1</v>
       </c>
       <c r="M50" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2">
         <v>0</v>
@@ -8361,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="AP50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ50" s="2">
         <v>-2</v>
@@ -8394,7 +8362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -8552,7 +8520,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -8710,962 +8678,962 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="B2:AZ52">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule priority="1" dxfId="0" type="expression">
       <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.51180550000000002" right="0.51180550000000002" top="0.78749999999999998" bottom="0.78749999999999998" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.5118055" right="0.5118055" top="0.7875" bottom="0.7875" header="0" footer="0"/>
+  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -825,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2">
         <v>-2</v>
@@ -944,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="2">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="2">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>-2</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q6" s="2">
         <v>-1</v>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q7" s="2">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="AA7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB7" s="2">
         <v>-1</v>
@@ -1576,7 +1576,7 @@
         <v>-1</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2">
         <v>-1</v>
@@ -1618,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="2">
         <v>1</v>
@@ -2447,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="AD13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" s="2">
         <v>1</v>
@@ -2513,7 +2513,7 @@
         <v>-1</v>
       </c>
       <c r="AZ13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -2829,7 +2829,7 @@
         <v>-2</v>
       </c>
       <c r="AZ15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -2885,10 +2885,10 @@
         <v>-2</v>
       </c>
       <c r="R16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T16" s="2">
         <v>0</v>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="2">
         <v>0</v>
@@ -2942,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="AK16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL16" s="2">
         <v>0</v>
@@ -2966,7 +2966,7 @@
         <v>-2</v>
       </c>
       <c r="AS16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT16" s="2">
         <v>-2</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="AV16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW16" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AX16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY16" s="2">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="2">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>-1</v>
       </c>
       <c r="AX17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY17" s="2">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -3353,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2">
         <v>1</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="2">
         <v>-1</v>
@@ -3747,7 +3747,7 @@
         <v>-1</v>
       </c>
       <c r="AP21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ21" s="2">
         <v>-1</v>
@@ -3791,7 +3791,7 @@
         <v>-1</v>
       </c>
       <c r="D22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -3827,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="2">
         <v>-2</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q24" s="2">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="2">
         <v>-1</v>
@@ -4590,7 +4590,7 @@
         <v>-1</v>
       </c>
       <c r="G27" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
       <c r="AH27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" s="2">
         <v>0</v>
@@ -5091,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="2">
         <v>-2</v>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -5407,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="2">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q33" s="2">
         <v>-2</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2">
         <v>-2</v>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="AA34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB34" s="2">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -6197,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="2">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>2</v>
       </c>
       <c r="AF39" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG39" s="2">
         <v>1</v>
@@ -6671,7 +6671,7 @@
         <v>-1</v>
       </c>
       <c r="P40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="2">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         <v>2</v>
       </c>
       <c r="AX41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY41" s="2">
         <v>-1</v>
@@ -7002,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="U42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V42" s="2">
         <v>0</v>
@@ -7408,7 +7408,7 @@
         <v>-1</v>
       </c>
       <c r="AY44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ44" s="2">
         <v>2</v>
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="2">
         <v>0</v>
@@ -7777,7 +7777,7 @@
         <v>-1</v>
       </c>
       <c r="P47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="2">
         <v>0</v>
@@ -8254,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="2">
         <v>-2</v>
@@ -8326,7 +8326,7 @@
         <v>-2</v>
       </c>
       <c r="AO50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP50" s="2">
         <v>0</v>
@@ -8493,7 +8493,7 @@
         <v>-1</v>
       </c>
       <c r="AR51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS51" s="2">
         <v>1</v>
@@ -8525,16 +8525,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2">
         <v>1</v>
@@ -8543,13 +8543,13 @@
         <v>2</v>
       </c>
       <c r="H52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="2">
         <v>1</v>
@@ -8558,16 +8558,16 @@
         <v>-1</v>
       </c>
       <c r="M52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N52" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="2">
         <v>-2</v>
@@ -8678,7 +8678,11 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="J53" s="2">
+        <v>-1</v>
+      </c>
+    </row>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -9628,8 +9632,13 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
+  <conditionalFormatting sqref="J53">
+    <cfRule priority="1" dxfId="0" type="expression">
+      <formula>J53&lt;&gt;-INDIRECT(ADDRESS(MATCH(J$1,$A:$A,0),MATCH($A53,$1:$1,0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:AZ52">
-    <cfRule priority="1" dxfId="0" type="expression">
+    <cfRule priority="2" dxfId="0" type="expression">
       <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Roadhog</t>
+  </si>
+  <si>
+    <t>Shion</t>
   </si>
   <si>
     <t>Sierra</t>
@@ -619,6 +622,9 @@
       <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -634,7 +640,7 @@
         <v>-1</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -751,30 +757,33 @@
         <v>0</v>
       </c>
       <c r="AR2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AT2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA2" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -891,22 +900,22 @@
         <v>0</v>
       </c>
       <c r="AL3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="2">
         <v>1</v>
       </c>
       <c r="AN3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" s="2">
         <v>0</v>
@@ -918,21 +927,24 @@
         <v>0</v>
       </c>
       <c r="AU3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" s="2">
         <v>0</v>
       </c>
       <c r="AX3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY3" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AZ3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA3" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -986,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R4" s="2">
         <v>-1</v>
@@ -1049,48 +1061,51 @@
         <v>0</v>
       </c>
       <c r="AL4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP4" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS4" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT4" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU4" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AV4" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW4" s="2">
         <v>-1</v>
       </c>
       <c r="AX4" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY4" s="2">
         <v>1</v>
       </c>
       <c r="AZ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1102,7 +1117,7 @@
         <v>-1</v>
       </c>
       <c r="C5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -1114,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2">
         <v>-1</v>
@@ -1123,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="2">
         <v>1</v>
@@ -1153,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2">
         <v>0</v>
@@ -1168,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="Y5" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Z5" s="2">
         <v>1</v>
@@ -1177,22 +1192,22 @@
         <v>0</v>
       </c>
       <c r="AB5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="2">
         <v>1</v>
       </c>
       <c r="AE5" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AF5" s="2">
         <v>1</v>
       </c>
       <c r="AG5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="2">
         <v>0</v>
@@ -1207,48 +1222,51 @@
         <v>0</v>
       </c>
       <c r="AL5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO5" s="2">
         <v>-1</v>
       </c>
       <c r="AP5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR5" s="2">
         <v>-1</v>
       </c>
       <c r="AS5" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AT5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX5" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AY5" s="2">
         <v>0</v>
       </c>
       <c r="AZ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1365,48 +1383,51 @@
         <v>0</v>
       </c>
       <c r="AL6" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AN6" s="2">
         <v>-1</v>
       </c>
       <c r="AO6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="2">
         <v>-1</v>
       </c>
       <c r="AS6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AT6" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AU6" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX6" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AY6" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AZ6" s="2">
+        <v>2</v>
+      </c>
+      <c r="BA6" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1529,19 +1550,19 @@
         <v>0</v>
       </c>
       <c r="AN7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP7" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ7" s="2">
         <v>-1</v>
       </c>
       <c r="AR7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS7" s="2">
         <v>1</v>
@@ -1550,21 +1571,24 @@
         <v>1</v>
       </c>
       <c r="AU7" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX7" s="2">
         <v>1</v>
       </c>
       <c r="AY7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1680,49 +1704,52 @@
       <c r="AK8" s="2">
         <v>0</v>
       </c>
-      <c r="AL8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="2">
-        <v>-1</v>
+      <c r="AL8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>0</v>
       </c>
       <c r="AN8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AV8" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA8" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1839,48 +1866,51 @@
         <v>0</v>
       </c>
       <c r="AL9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AR9" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX9" s="2">
         <v>-1</v>
       </c>
       <c r="AY9" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AZ9" s="2">
+        <v>-2</v>
+      </c>
+      <c r="BA9" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -1898,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
         <v>2</v>
@@ -1997,48 +2027,51 @@
         <v>0</v>
       </c>
       <c r="AL10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ10" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AR10" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT10" s="2">
         <v>-1</v>
       </c>
       <c r="AU10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AW10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -2056,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <v>-1</v>
@@ -2128,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AD11" s="2">
         <v>0</v>
@@ -2155,25 +2188,25 @@
         <v>0</v>
       </c>
       <c r="AL11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO11" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AQ11" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AR11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS11" s="2">
         <v>0</v>
@@ -2182,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" s="2">
         <v>1</v>
@@ -2191,12 +2224,15 @@
         <v>1</v>
       </c>
       <c r="AX11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2310,51 +2346,54 @@
         <v>1</v>
       </c>
       <c r="AK12" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP12" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AQ12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS12" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AT12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AV12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW12" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX12" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ12" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2447,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="AD13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="2">
         <v>1</v>
@@ -2483,16 +2522,16 @@
         <v>0</v>
       </c>
       <c r="AP13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="2">
         <v>1</v>
       </c>
       <c r="AR13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT13" s="2">
         <v>-1</v>
@@ -2501,7 +2540,7 @@
         <v>-1</v>
       </c>
       <c r="AV13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW13" s="2">
         <v>0</v>
@@ -2510,9 +2549,12 @@
         <v>0</v>
       </c>
       <c r="AY13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA13" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2629,48 +2671,51 @@
         <v>0</v>
       </c>
       <c r="AL14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="2">
         <v>1</v>
       </c>
       <c r="AN14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" s="2">
         <v>0</v>
       </c>
       <c r="AP14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" s="2">
         <v>0</v>
       </c>
       <c r="AS14" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AT14" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW14" s="2">
         <v>-1</v>
       </c>
       <c r="AX14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2790,45 +2835,48 @@
         <v>0</v>
       </c>
       <c r="AM15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="2">
         <v>1</v>
       </c>
       <c r="AO15" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP15" s="2">
         <v>-1</v>
       </c>
       <c r="AQ15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR15" s="2">
         <v>0</v>
       </c>
       <c r="AS15" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV15" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AW15" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AX15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY15" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AZ15" s="2">
+        <v>-2</v>
+      </c>
+      <c r="BA15" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2900,7 +2948,7 @@
         <v>-2</v>
       </c>
       <c r="W16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="2">
         <v>1</v>
@@ -2942,52 +2990,55 @@
         <v>1</v>
       </c>
       <c r="AK16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP16" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ16" s="2">
         <v>1</v>
       </c>
       <c r="AR16" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AS16" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AT16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU16" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AX16" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AY16" s="2">
         <v>0</v>
       </c>
       <c r="AZ16" s="2">
         <v>0</v>
+      </c>
+      <c r="BA16" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -3001,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -3103,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="AL17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN17" s="2">
         <v>-1</v>
@@ -3115,25 +3166,25 @@
         <v>-1</v>
       </c>
       <c r="AP17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ17" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT17" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW17" s="2">
         <v>-1</v>
@@ -3142,9 +3193,12 @@
         <v>-1</v>
       </c>
       <c r="AY17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3267,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="2">
         <v>1</v>
@@ -3276,33 +3330,36 @@
         <v>1</v>
       </c>
       <c r="AQ18" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR18" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS18" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AT18" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AU18" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW18" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -3320,7 +3377,7 @@
         <v>-1</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -3419,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO19" s="2">
         <v>0</v>
       </c>
       <c r="AP19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="2">
         <v>1</v>
@@ -3440,27 +3497,30 @@
         <v>1</v>
       </c>
       <c r="AS19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT19" s="2">
         <v>0</v>
       </c>
       <c r="AU19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW19" s="2">
         <v>0</v>
       </c>
       <c r="AX19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY19" s="2">
         <v>1</v>
       </c>
       <c r="AZ19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3577,22 +3637,22 @@
         <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM20" s="2">
         <v>-1</v>
       </c>
       <c r="AN20" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO20" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AP20" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR20" s="2">
         <v>0</v>
@@ -3604,21 +3664,24 @@
         <v>0</v>
       </c>
       <c r="AU20" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW20" s="2">
         <v>0</v>
       </c>
       <c r="AX20" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AY20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AZ20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA20" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -3738,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="AM21" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="2">
         <v>-1</v>
@@ -3747,36 +3810,39 @@
         <v>-1</v>
       </c>
       <c r="AP21" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AQ21" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AR21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AV21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" s="2">
         <v>1</v>
       </c>
       <c r="AY21" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA21" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -3893,48 +3959,51 @@
         <v>0</v>
       </c>
       <c r="AL22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" s="2">
         <v>1</v>
       </c>
       <c r="AN22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR22" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT22" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AU22" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AV22" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AW22" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AX22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY22" s="2">
         <v>0</v>
       </c>
       <c r="AZ22" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3985,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q23" s="2">
         <v>-2</v>
@@ -4051,48 +4120,51 @@
         <v>0</v>
       </c>
       <c r="AL23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN23" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AO23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR23" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AS23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU23" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AV23" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX23" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AY23" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AZ23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA23" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4209,28 +4281,28 @@
         <v>0</v>
       </c>
       <c r="AL24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="2">
         <v>-1</v>
       </c>
       <c r="AP24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR24" s="2">
         <v>-1</v>
       </c>
       <c r="AS24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT24" s="2">
         <v>0</v>
@@ -4245,12 +4317,15 @@
         <v>0</v>
       </c>
       <c r="AX24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY24" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AZ24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA24" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4376,39 +4451,42 @@
         <v>0</v>
       </c>
       <c r="AO25" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP25" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ25" s="2">
         <v>0</v>
       </c>
       <c r="AR25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS25" s="2">
         <v>1</v>
       </c>
       <c r="AT25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" s="2">
         <v>0</v>
       </c>
       <c r="AV25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY25" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA25" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4426,7 +4504,7 @@
         <v>-2</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
@@ -4525,48 +4603,51 @@
         <v>0</v>
       </c>
       <c r="AL26" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM26" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AN26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" s="2">
         <v>1</v>
       </c>
       <c r="AP26" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR26" s="2">
         <v>0</v>
       </c>
       <c r="AS26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT26" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV26" s="2">
         <v>0</v>
       </c>
       <c r="AW26" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY26" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA26" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4683,48 +4764,51 @@
         <v>0</v>
       </c>
       <c r="AL27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP27" s="2">
         <v>1</v>
       </c>
       <c r="AQ27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT27" s="2">
         <v>0</v>
       </c>
       <c r="AU27" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV27" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW27" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX27" s="2">
         <v>-1</v>
       </c>
       <c r="AY27" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AZ27" s="2">
+        <v>2</v>
+      </c>
+      <c r="BA27" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4844,19 +4928,19 @@
         <v>0</v>
       </c>
       <c r="AM28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="2">
         <v>1</v>
       </c>
       <c r="AO28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP28" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="2">
         <v>0</v>
@@ -4865,24 +4949,27 @@
         <v>0</v>
       </c>
       <c r="AT28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU28" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW28" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AX28" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AY28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA28" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -4900,7 +4987,7 @@
         <v>-1</v>
       </c>
       <c r="E29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
@@ -4918,7 +5005,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2">
         <v>-1</v>
@@ -5002,45 +5089,48 @@
         <v>0</v>
       </c>
       <c r="AM29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO29" s="2">
         <v>1</v>
       </c>
       <c r="AP29" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ29" s="2">
         <v>-1</v>
       </c>
       <c r="AR29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS29" s="2">
         <v>1</v>
       </c>
       <c r="AT29" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY29" s="2">
         <v>1</v>
       </c>
       <c r="AZ29" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA29" s="2">
         <v>-2</v>
       </c>
     </row>
@@ -5157,37 +5247,37 @@
         <v>0</v>
       </c>
       <c r="AL30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AN30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP30" s="2">
         <v>-1</v>
       </c>
       <c r="AQ30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS30" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT30" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU30" s="2">
         <v>-1</v>
       </c>
       <c r="AV30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW30" s="2">
         <v>0</v>
@@ -5196,9 +5286,12 @@
         <v>0</v>
       </c>
       <c r="AY30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA30" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5216,7 +5309,7 @@
         <v>-2</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
@@ -5318,34 +5411,34 @@
         <v>0</v>
       </c>
       <c r="AM31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AR31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW31" s="2">
         <v>1</v>
@@ -5354,9 +5447,12 @@
         <v>1</v>
       </c>
       <c r="AY31" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AZ31" s="2">
+        <v>-2</v>
+      </c>
+      <c r="BA31" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5374,7 +5470,7 @@
         <v>-2</v>
       </c>
       <c r="E32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -5473,25 +5569,25 @@
         <v>0</v>
       </c>
       <c r="AL32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="2">
         <v>1</v>
       </c>
       <c r="AN32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP32" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" s="2">
         <v>1</v>
@@ -5500,10 +5596,10 @@
         <v>1</v>
       </c>
       <c r="AU32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV32" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW32" s="2">
         <v>-1</v>
@@ -5512,9 +5608,12 @@
         <v>-1</v>
       </c>
       <c r="AY32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ32" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5631,48 +5730,51 @@
         <v>0</v>
       </c>
       <c r="AL33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM33" s="2">
         <v>1</v>
       </c>
       <c r="AN33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="2">
         <v>0</v>
       </c>
       <c r="AP33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ33" s="2">
         <v>-1</v>
       </c>
       <c r="AR33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW33" s="2">
         <v>0</v>
       </c>
       <c r="AX33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY33" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA33" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5789,48 +5891,51 @@
         <v>0</v>
       </c>
       <c r="AL34" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM34" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AN34" s="2">
         <v>0</v>
       </c>
       <c r="AO34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS34" s="2">
         <v>-1</v>
       </c>
       <c r="AT34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW34" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AX34" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AY34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA34" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -5947,48 +6052,51 @@
         <v>0</v>
       </c>
       <c r="AL35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AN35" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO35" s="2">
         <v>0</v>
       </c>
       <c r="AP35" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AQ35" s="2">
         <v>-2</v>
       </c>
       <c r="AR35" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU35" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW35" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX35" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AY35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA35" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -6105,48 +6213,51 @@
         <v>0</v>
       </c>
       <c r="AL36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM36" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AN36" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP36" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR36" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS36" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AT36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY36" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ36" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA36" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -6154,9 +6265,7 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
-        <v>0</v>
-      </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2">
         <v>0</v>
       </c>
@@ -6185,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -6197,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="2">
         <v>0</v>
@@ -6272,10 +6381,10 @@
         <v>0</v>
       </c>
       <c r="AO37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ37" s="2">
         <v>0</v>
@@ -6305,6 +6414,9 @@
         <v>0</v>
       </c>
       <c r="AZ37" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA37" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6316,16 +6428,16 @@
         <v>0</v>
       </c>
       <c r="C38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -6334,61 +6446,61 @@
         <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2">
         <v>0</v>
       </c>
       <c r="P38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="2">
         <v>0</v>
       </c>
       <c r="S38" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="2">
         <v>0</v>
       </c>
       <c r="V38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X38" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="2">
         <v>0</v>
       </c>
       <c r="Z38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="2">
         <v>0</v>
@@ -6397,25 +6509,25 @@
         <v>0</v>
       </c>
       <c r="AD38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="2">
         <v>0</v>
       </c>
       <c r="AF38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="2">
         <v>0</v>
@@ -6427,13 +6539,13 @@
         <v>0</v>
       </c>
       <c r="AN38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP38" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AQ38" s="2">
         <v>1</v>
@@ -6442,13 +6554,13 @@
         <v>0</v>
       </c>
       <c r="AS38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT38" s="2">
         <v>0</v>
       </c>
       <c r="AU38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="2">
         <v>0</v>
@@ -6460,9 +6572,12 @@
         <v>0</v>
       </c>
       <c r="AY38" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AZ38" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA38" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6471,37 +6586,37 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="2">
         <v>-1</v>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
       <c r="G39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
         <v>-1</v>
       </c>
       <c r="J39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M39" s="2">
         <v>0</v>
@@ -6510,43 +6625,43 @@
         <v>-1</v>
       </c>
       <c r="O39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X39" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="2">
         <v>2</v>
       </c>
       <c r="AA39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB39" s="2">
         <v>0</v>
@@ -6558,22 +6673,22 @@
         <v>1</v>
       </c>
       <c r="AE39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="2">
         <v>-1</v>
       </c>
       <c r="AG39" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI39" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AJ39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK39" s="2">
         <v>0</v>
@@ -6585,43 +6700,46 @@
         <v>0</v>
       </c>
       <c r="AN39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP39" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AQ39" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AR39" s="2">
         <v>1</v>
       </c>
       <c r="AS39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AT39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV39" s="2">
         <v>1</v>
       </c>
       <c r="AW39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX39" s="2">
         <v>0</v>
       </c>
       <c r="AY39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ39" s="2">
-        <v>1</v>
+        <v>-2</v>
+      </c>
+      <c r="BA39" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -6632,55 +6750,55 @@
         <v>1</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
       </c>
       <c r="H40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J40" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2">
         <v>-2</v>
       </c>
       <c r="L40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2">
         <v>0</v>
       </c>
       <c r="N40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O40" s="2">
         <v>-1</v>
       </c>
       <c r="P40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="2">
         <v>-1</v>
       </c>
       <c r="S40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T40" s="2">
         <v>0</v>
@@ -6689,40 +6807,40 @@
         <v>1</v>
       </c>
       <c r="V40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="2">
         <v>-1</v>
       </c>
       <c r="Z40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="2">
         <v>0</v>
       </c>
       <c r="AC40" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD40" s="2">
         <v>1</v>
       </c>
       <c r="AE40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" s="2">
         <v>1</v>
@@ -6731,54 +6849,57 @@
         <v>1</v>
       </c>
       <c r="AJ40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK40" s="2">
         <v>0</v>
       </c>
       <c r="AL40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="2">
         <v>0</v>
       </c>
       <c r="AO40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR40" s="2">
         <v>1</v>
       </c>
       <c r="AS40" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT40" s="2">
         <v>-1</v>
       </c>
       <c r="AU40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV40" s="2">
         <v>-1</v>
       </c>
       <c r="AW40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ40" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA40" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6787,61 +6908,61 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J41" s="2">
         <v>-1</v>
       </c>
       <c r="K41" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2">
         <v>0</v>
       </c>
       <c r="N41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="2">
         <v>-1</v>
       </c>
       <c r="S41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U41" s="2">
         <v>1</v>
@@ -6853,91 +6974,94 @@
         <v>-1</v>
       </c>
       <c r="X41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Z41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AB41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AD41" s="2">
         <v>1</v>
       </c>
       <c r="AE41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" s="2">
         <v>0</v>
       </c>
       <c r="AH41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK41" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AN41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO41" s="2">
         <v>0</v>
       </c>
       <c r="AP41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ41" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR41" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AS41" s="2">
         <v>1</v>
       </c>
       <c r="AT41" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AU41" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AV41" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW41" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AX41" s="2">
         <v>-1</v>
       </c>
       <c r="AY41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ41" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="BA41" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -6948,154 +7072,157 @@
         <v>0</v>
       </c>
       <c r="C42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="H42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K42" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2">
         <v>1</v>
       </c>
       <c r="P42" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R42" s="2">
         <v>-1</v>
       </c>
       <c r="S42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U42" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA42" s="2">
         <v>-1</v>
       </c>
       <c r="AB42" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD42" s="2">
         <v>1</v>
       </c>
       <c r="AE42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF42" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL42" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="AM42" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO42" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AP42" s="2">
         <v>0</v>
       </c>
       <c r="AQ42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT42" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AU42" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AV42" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW42" s="2">
         <v>-2</v>
       </c>
       <c r="AX42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AZ42" s="2">
         <v>-1</v>
+      </c>
+      <c r="BA42" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -7106,106 +7233,106 @@
         <v>0</v>
       </c>
       <c r="C43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M43" s="2">
         <v>-1</v>
       </c>
       <c r="N43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="2">
         <v>-1</v>
       </c>
       <c r="Q43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S43" s="2">
         <v>-1</v>
       </c>
       <c r="T43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W43" s="2">
         <v>0</v>
       </c>
       <c r="X43" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="2">
         <v>1</v>
       </c>
       <c r="AA43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" s="2">
         <v>1</v>
       </c>
       <c r="AF43" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AG43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" s="2">
         <v>1</v>
       </c>
       <c r="AI43" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ43" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AK43" s="2">
         <v>0</v>
@@ -7214,46 +7341,49 @@
         <v>-1</v>
       </c>
       <c r="AM43" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ43" s="2">
         <v>0</v>
       </c>
       <c r="AR43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT43" s="2">
         <v>0</v>
       </c>
       <c r="AU43" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV43" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX43" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AY43" s="2">
         <v>0</v>
       </c>
       <c r="AZ43" s="2">
         <v>1</v>
+      </c>
+      <c r="BA43" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -7261,13 +7391,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
@@ -7276,13 +7406,13 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -7291,25 +7421,25 @@
         <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q44" s="2">
         <v>0</v>
       </c>
       <c r="R44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="2">
         <v>-1</v>
@@ -7318,40 +7448,40 @@
         <v>0</v>
       </c>
       <c r="U44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W44" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="X44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y44" s="2">
         <v>-1</v>
       </c>
       <c r="Z44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AG44" s="2">
         <v>0</v>
@@ -7363,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AK44" s="2">
         <v>0</v>
@@ -7375,25 +7505,25 @@
         <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR44" s="2">
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU44" s="2">
         <v>0</v>
@@ -7402,16 +7532,19 @@
         <v>0</v>
       </c>
       <c r="AW44" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AX44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ44" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="BA44" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -7422,49 +7555,49 @@
         <v>1</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I45" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="2">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="2">
         <v>0</v>
@@ -7476,25 +7609,25 @@
         <v>0</v>
       </c>
       <c r="U45" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z45" s="2">
         <v>0</v>
       </c>
       <c r="AA45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" s="2">
         <v>0</v>
@@ -7506,7 +7639,7 @@
         <v>1</v>
       </c>
       <c r="AE45" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="2">
         <v>-1</v>
@@ -7515,46 +7648,46 @@
         <v>0</v>
       </c>
       <c r="AH45" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AK45" s="2">
         <v>0</v>
       </c>
       <c r="AL45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO45" s="2">
         <v>-1</v>
       </c>
       <c r="AP45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS45" s="2">
         <v>0</v>
       </c>
       <c r="AT45" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV45" s="2">
         <v>0</v>
@@ -7563,13 +7696,16 @@
         <v>0</v>
       </c>
       <c r="AX45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY45" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AZ45" s="2">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="BA45" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -7577,37 +7713,37 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I46" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M46" s="2">
         <v>1</v>
@@ -7616,25 +7752,25 @@
         <v>-1</v>
       </c>
       <c r="O46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T46" s="2">
         <v>0</v>
       </c>
       <c r="U46" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V46" s="2">
         <v>0</v>
@@ -7649,22 +7785,22 @@
         <v>0</v>
       </c>
       <c r="Z46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="2">
         <v>0</v>
       </c>
       <c r="AB46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD46" s="2">
         <v>1</v>
       </c>
       <c r="AE46" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF46" s="2">
         <v>-1</v>
@@ -7676,10 +7812,10 @@
         <v>-1</v>
       </c>
       <c r="AI46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ46" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK46" s="2">
         <v>0</v>
@@ -7688,46 +7824,49 @@
         <v>0</v>
       </c>
       <c r="AM46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP46" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AQ46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AS46" s="2">
         <v>0</v>
       </c>
       <c r="AT46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV46" s="2">
         <v>0</v>
       </c>
       <c r="AW46" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AX46" s="2">
         <v>0</v>
       </c>
       <c r="AY46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BA46" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -7735,70 +7874,70 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="2">
         <v>-1</v>
       </c>
       <c r="F47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
       </c>
       <c r="K47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M47" s="2">
         <v>1</v>
       </c>
       <c r="N47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P47" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="2">
         <v>0</v>
       </c>
       <c r="R47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="2">
         <v>0</v>
       </c>
       <c r="U47" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="V47" s="2">
         <v>0</v>
       </c>
       <c r="W47" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X47" s="2">
         <v>0</v>
@@ -7810,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="AA47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" s="2">
         <v>0</v>
@@ -7825,52 +7964,52 @@
         <v>0</v>
       </c>
       <c r="AF47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK47" s="2">
         <v>0</v>
       </c>
       <c r="AL47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AQ47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AT47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV47" s="2">
         <v>1</v>
@@ -7879,13 +8018,16 @@
         <v>0</v>
       </c>
       <c r="AX47" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AY47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" s="2">
         <v>-1</v>
+      </c>
+      <c r="BA47" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -7893,49 +8035,49 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2">
         <v>1</v>
       </c>
       <c r="F48" s="2">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2">
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="P48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="2">
         <v>0</v>
@@ -7947,55 +8089,55 @@
         <v>0</v>
       </c>
       <c r="T48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AB48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE48" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AG48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ48" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AK48" s="2">
         <v>0</v>
@@ -8004,22 +8146,22 @@
         <v>0</v>
       </c>
       <c r="AM48" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN48" s="2">
         <v>1</v>
       </c>
       <c r="AO48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP48" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AQ48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AR48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS48" s="2">
         <v>0</v>
@@ -8028,22 +8170,25 @@
         <v>-1</v>
       </c>
       <c r="AU48" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AV48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY48" s="2">
         <v>0</v>
       </c>
       <c r="AZ48" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="BA48" s="2">
+        <v>-1</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -8060,61 +8205,61 @@
         <v>1</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M49" s="2">
         <v>0</v>
       </c>
       <c r="N49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="X49" s="2">
         <v>1</v>
@@ -8126,34 +8271,34 @@
         <v>-2</v>
       </c>
       <c r="AA49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB49" s="2">
         <v>1</v>
       </c>
       <c r="AC49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AD49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AF49" s="2">
         <v>-2</v>
       </c>
       <c r="AG49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AI49" s="2">
         <v>0</v>
       </c>
       <c r="AJ49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK49" s="2">
         <v>0</v>
@@ -8162,19 +8307,19 @@
         <v>0</v>
       </c>
       <c r="AM49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AP49" s="2">
         <v>2</v>
       </c>
       <c r="AQ49" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AR49" s="2">
         <v>-1</v>
@@ -8186,7 +8331,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AV49" s="2">
         <v>1</v>
@@ -8195,12 +8340,15 @@
         <v>0</v>
       </c>
       <c r="AX49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AZ49" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA49" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8209,76 +8357,76 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G50" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2">
         <v>0</v>
       </c>
       <c r="N50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P50" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S50" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="T50" s="2">
         <v>-2</v>
       </c>
       <c r="U50" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W50" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="2">
         <v>-2</v>
@@ -8287,31 +8435,31 @@
         <v>1</v>
       </c>
       <c r="AB50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AC50" s="2">
         <v>-2</v>
       </c>
       <c r="AD50" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE50" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AF50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AG50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AH50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AI50" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK50" s="2">
         <v>0</v>
@@ -8320,46 +8468,49 @@
         <v>0</v>
       </c>
       <c r="AM50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN50" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AO50" s="2">
         <v>1</v>
       </c>
       <c r="AP50" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ50" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AR50" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AS50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT50" s="2">
         <v>0</v>
       </c>
       <c r="AU50" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AV50" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX50" s="2">
         <v>0</v>
       </c>
       <c r="AY50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ50" s="2">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="BA50" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -8367,10 +8518,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D51" s="2">
         <v>-1</v>
@@ -8379,121 +8530,121 @@
         <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="2">
         <v>-1</v>
       </c>
       <c r="K51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="P51" s="2">
         <v>0</v>
       </c>
       <c r="Q51" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S51" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="T51" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="U51" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="V51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X51" s="2">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Y51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Z51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AA51" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AB51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AC51" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AD51" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH51" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AI51" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AJ51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK51" s="2">
         <v>0</v>
       </c>
       <c r="AL51" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN51" s="2">
         <v>-1</v>
       </c>
       <c r="AO51" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AP51" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR51" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS51" s="2">
         <v>1</v>
@@ -8502,22 +8653,25 @@
         <v>0</v>
       </c>
       <c r="AU51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV51" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AW51" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AX51" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ51" s="2">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BA51" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
@@ -8525,52 +8679,52 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G52" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K52" s="2">
         <v>1</v>
       </c>
       <c r="L52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="P52" s="2">
         <v>0</v>
       </c>
       <c r="Q52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R52" s="2">
         <v>0</v>
@@ -8585,7 +8739,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="2">
         <v>1</v>
@@ -8594,37 +8748,37 @@
         <v>2</v>
       </c>
       <c r="Y52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" s="2">
         <v>0</v>
       </c>
       <c r="AA52" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AB52" s="2">
         <v>0</v>
       </c>
       <c r="AC52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG52" s="2">
         <v>0</v>
       </c>
       <c r="AH52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="2">
         <v>1</v>
@@ -8636,54 +8790,215 @@
         <v>0</v>
       </c>
       <c r="AM52" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AP52" s="2">
         <v>1</v>
       </c>
       <c r="AQ52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AR52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT52" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AU52" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX52" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AY52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ52" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA52" s="2">
         <v>-1</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2</v>
+      </c>
+      <c r="H53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I53" s="2">
+        <v>-2</v>
+      </c>
       <c r="J53" s="2">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="M53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="O53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="P53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="T53" s="2">
+        <v>2</v>
+      </c>
+      <c r="U53" s="2">
+        <v>1</v>
+      </c>
+      <c r="V53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="W53" s="2">
+        <v>1</v>
+      </c>
+      <c r="X53" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y53" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AQ53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AS53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AT53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU53" s="2">
+        <v>-2</v>
+      </c>
+      <c r="AV53" s="2">
+        <v>2</v>
+      </c>
+      <c r="AW53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AX53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AY53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="2">
+        <v>-1</v>
+      </c>
+      <c r="BA53" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="J54" s="2"/>
+    </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1"/>
@@ -9631,13 +9946,14 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="J53">
+  <conditionalFormatting sqref="J54">
     <cfRule priority="1" dxfId="0" type="expression">
-      <formula>J53&lt;&gt;-INDIRECT(ADDRESS(MATCH(J$1,$A:$A,0),MATCH($A53,$1:$1,0)))</formula>
+      <formula>J54&lt;&gt;-INDIRECT(ADDRESS(MATCH(J$1,$A:$A,0),MATCH($A54,$1:$1,0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:AZ52">
+  <conditionalFormatting sqref="B2:BA53">
     <cfRule priority="2" dxfId="0" type="expression">
       <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
     </cfRule>

--- a/dist/OWPick/_internal/heroes enemy.xlsx
+++ b/dist/OWPick/_internal/heroes enemy.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projetos\Overwatch-Best-Picks\"/>
@@ -637,28 +636,28 @@
         <v>-1</v>
       </c>
       <c r="D2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J2" s="2">
         <v>-1</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -676,10 +675,10 @@
         <v>-1</v>
       </c>
       <c r="Q2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
         <v>1</v>
@@ -691,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W2" s="2">
         <v>0</v>
@@ -709,25 +708,25 @@
         <v>-1</v>
       </c>
       <c r="AB2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="2">
         <v>1</v>
       </c>
       <c r="AD2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AF2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AG2" s="2">
         <v>0</v>
       </c>
       <c r="AH2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
@@ -736,7 +735,7 @@
         <v>2</v>
       </c>
       <c r="AK2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL2" s="2">
         <v>0</v>
@@ -745,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="AN2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP2" s="2">
         <v>0</v>
@@ -763,16 +762,16 @@
         <v>-1</v>
       </c>
       <c r="AT2" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AU2" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV2" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AW2" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AX2" s="2">
         <v>0</v>
@@ -784,7 +783,7 @@
         <v>-1</v>
       </c>
       <c r="BA2" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -879,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF3" s="2">
         <v>-1</v>
@@ -900,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM3" s="2">
         <v>1</v>
@@ -953,7 +952,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
         <v>-1</v>
@@ -1114,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1222,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM5" s="2">
         <v>1</v>
@@ -1275,7 +1274,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1380,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="AK6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM6" s="2">
         <v>-2</v>
@@ -1436,7 +1435,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1523,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF7" s="2">
         <v>1</v>
@@ -1544,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="2">
         <v>0</v>
@@ -1597,7 +1596,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
@@ -1702,10 +1701,10 @@
         <v>-1</v>
       </c>
       <c r="AK8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM8" s="3">
         <v>0</v>
@@ -1758,7 +1757,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2">
         <v>-2</v>
@@ -1845,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="2">
         <v>1</v>
@@ -1863,10 +1862,10 @@
         <v>1</v>
       </c>
       <c r="AK9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM9" s="2">
         <v>1</v>
@@ -1919,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
@@ -2006,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="2">
         <v>1</v>
@@ -2185,10 +2184,10 @@
         <v>-2</v>
       </c>
       <c r="AK11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM11" s="2">
         <v>1</v>
@@ -2349,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="AL12" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM12" s="2">
         <v>1</v>
@@ -2510,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="AL13" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM13" s="2">
         <v>0</v>
@@ -2563,7 +2562,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -2650,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="AE14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" s="2">
         <v>-1</v>
@@ -2832,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="AL15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM15" s="2">
         <v>0</v>
@@ -3133,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="AE17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="2">
         <v>-1</v>
@@ -3154,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="AL17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" s="2">
         <v>-1</v>
@@ -3294,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="AE18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF18" s="2">
         <v>0</v>
@@ -3312,10 +3311,10 @@
         <v>-1</v>
       </c>
       <c r="AK18" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL18" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM18" s="2">
         <v>0</v>
@@ -3368,7 +3367,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -3455,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="2">
         <v>1</v>
@@ -3476,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM19" s="2">
         <v>2</v>
@@ -3616,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="AE20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF20" s="2">
         <v>0</v>
@@ -3637,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" s="2">
         <v>-1</v>
@@ -3777,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="AE21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF21" s="2">
         <v>-1</v>
@@ -3798,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="AL21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" s="2">
         <v>0</v>
@@ -3938,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="AE22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="2">
         <v>-1</v>
@@ -3959,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="AL22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM22" s="2">
         <v>1</v>
@@ -4099,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="AE23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="2">
         <v>0</v>
@@ -4260,7 +4259,7 @@
         <v>-1</v>
       </c>
       <c r="AE24" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF24" s="2">
         <v>-1</v>
@@ -4421,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="AE25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" s="2">
         <v>1</v>
@@ -4439,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="AK25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM25" s="2">
         <v>0</v>
@@ -4582,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="AE26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF26" s="2">
         <v>-1</v>
@@ -4603,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="AL26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM26" s="2">
         <v>-2</v>
@@ -4904,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="AE28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="2">
         <v>1</v>
@@ -4925,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="AL28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" s="2">
         <v>0</v>
@@ -5065,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="AE29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AF29" s="2">
         <v>1</v>
@@ -5139,7 +5138,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -5226,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AE30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF30" s="2">
         <v>-1</v>
@@ -5303,7 +5302,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2">
         <v>-2</v>
@@ -5312,7 +5311,7 @@
         <v>-1</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -5324,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
@@ -5345,10 +5344,10 @@
         <v>-1</v>
       </c>
       <c r="Q31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S31" s="2">
         <v>0</v>
@@ -5384,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="AD31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="2">
         <v>0</v>
@@ -5393,7 +5392,7 @@
         <v>-2</v>
       </c>
       <c r="AG31" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="2">
         <v>0</v>
@@ -5408,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="AL31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM31" s="2">
         <v>0</v>
@@ -5426,13 +5425,13 @@
         <v>-1</v>
       </c>
       <c r="AR31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS31" s="2">
         <v>0</v>
       </c>
       <c r="AT31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" s="2">
         <v>0</v>
@@ -5453,7 +5452,7 @@
         <v>-2</v>
       </c>
       <c r="BA31" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -5461,7 +5460,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -5548,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="AE32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" s="2">
         <v>0</v>
@@ -5709,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="AE33" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="2">
         <v>0</v>
@@ -5730,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM33" s="2">
         <v>1</v>
@@ -5888,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="AK34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL34" s="2">
         <v>0</v>
@@ -6052,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="AL35" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35" s="2">
         <v>1</v>
@@ -6210,10 +6209,10 @@
         <v>0</v>
       </c>
       <c r="AK36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" s="2">
         <v>-1</v>
@@ -6265,7 +6264,9 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
@@ -6276,22 +6277,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
@@ -6303,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="2">
         <v>0</v>
@@ -6312,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="R37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="2">
         <v>0</v>
@@ -6327,13 +6328,13 @@
         <v>0</v>
       </c>
       <c r="W37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X37" s="2">
         <v>0</v>
       </c>
       <c r="Y37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Z37" s="2">
         <v>0</v>
@@ -6342,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC37" s="2">
         <v>0</v>
@@ -6360,16 +6361,16 @@
         <v>0</v>
       </c>
       <c r="AH37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AI37" s="2">
         <v>0</v>
       </c>
       <c r="AJ37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AK37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL37" s="2">
         <v>0</v>
@@ -6378,22 +6379,22 @@
         <v>0</v>
       </c>
       <c r="AN37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO37" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ37" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR37" s="2">
         <v>0</v>
       </c>
       <c r="AS37" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT37" s="2">
         <v>0</v>
@@ -6428,55 +6429,55 @@
         <v>0</v>
       </c>
       <c r="C38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="2">
         <v>0</v>
       </c>
       <c r="R38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T38" s="2">
         <v>0</v>
@@ -6485,43 +6486,43 @@
         <v>0</v>
       </c>
       <c r="V38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="2">
         <v>0</v>
       </c>
       <c r="X38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y38" s="2">
         <v>0</v>
       </c>
       <c r="Z38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="2">
         <v>0</v>
       </c>
       <c r="AG38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" s="2">
         <v>0</v>
@@ -6530,28 +6531,28 @@
         <v>0</v>
       </c>
       <c r="AK38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" s="2">
         <v>0</v>
       </c>
       <c r="AM38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ38" s="2">
         <v>1</v>
       </c>
       <c r="AR38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS38" s="2">
         <v>0</v>
@@ -6560,25 +6561,25 @@
         <v>0</v>
       </c>
       <c r="AU38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV38" s="2">
         <v>0</v>
       </c>
       <c r="AW38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ38" s="2">
         <v>0</v>
       </c>
       <c r="BA38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -6694,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="AL39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" s="2">
         <v>0</v>
@@ -6834,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="AE40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF40" s="2">
         <v>-1</v>
@@ -6852,7 +6853,7 @@
         <v>2</v>
       </c>
       <c r="AK40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" s="2">
         <v>0</v>
@@ -7013,10 +7014,10 @@
         <v>0</v>
       </c>
       <c r="AK41" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM41" s="2">
         <v>-1</v>
@@ -7174,10 +7175,10 @@
         <v>1</v>
       </c>
       <c r="AK42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL42" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM42" s="2">
         <v>2</v>
@@ -7338,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="AL43" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM43" s="2">
         <v>2</v>
@@ -7478,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="AE44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="2">
         <v>1</v>
@@ -7499,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="AL44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM44" s="2">
         <v>-1</v>
@@ -7657,10 +7658,10 @@
         <v>1</v>
       </c>
       <c r="AK45" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" s="2">
         <v>0</v>
@@ -7874,7 +7875,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="2">
         <v>-1</v>
@@ -8035,7 +8036,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2">
         <v>2</v>
@@ -8122,7 +8123,7 @@
         <v>1</v>
       </c>
       <c r="AE48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF48" s="2">
         <v>1</v>
@@ -8304,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="AL49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM49" s="2">
         <v>0</v>
@@ -8357,7 +8358,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -8444,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="AE50" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AF50" s="2">
         <v>-2</v>
@@ -8465,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="AL50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM50" s="2">
         <v>0</v>
@@ -8626,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="AL51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM51" s="2">
         <v>0</v>
@@ -8766,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="AE52" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF52" s="2">
         <v>-1</v>
@@ -8945,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="AK53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL53" s="2">
         <v>0</v>
@@ -9959,6 +9960,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5118055" right="0.5118055" top="0.7875" bottom="0.7875" header="0" footer="0"/>
-  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>